--- a/2026/EL MIRADOR/Abril/Abril - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Abril/Abril - EL MIRADOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Abril\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6321215C-6B87-4CD0-866C-EF015505E084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB035C5B-405A-418B-9573-A6AA325E2CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -24,16 +24,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$129</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="409">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1127,42 +1122,6 @@
     <t>MOTIVO DE LA QUEJA:</t>
   </si>
   <si>
-    <t>6D</t>
-  </si>
-  <si>
-    <t>Anchipi</t>
-  </si>
-  <si>
-    <t>El mes pasado en la planilla ARBA el pago $39.000 y no se le restaron de la columna "saldo total" para abonar - El adjudica que lo debe abonar el propietario anterior el restante.</t>
-  </si>
-  <si>
-    <t>Local 1</t>
-  </si>
-  <si>
-    <t>$269.608 el 08/04</t>
-  </si>
-  <si>
-    <t>Local 2</t>
-  </si>
-  <si>
-    <t>$148.104 el 17/04</t>
-  </si>
-  <si>
-    <t>Deposito $300.000 y $30.000 23/04</t>
-  </si>
-  <si>
-    <t>No sabemos</t>
-  </si>
-  <si>
-    <t>Veronica(?)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2E, 6E, 9E y cochera 12</t>
-  </si>
-  <si>
-    <t>Deposito $673.000 el 16/04</t>
-  </si>
-  <si>
     <t>VTO 15/05</t>
   </si>
   <si>
@@ -1193,12 +1152,6 @@
     <t>Transf 15/04</t>
   </si>
   <si>
-    <t>7D</t>
-  </si>
-  <si>
-    <t>Cambiar titularidad x Walter nose</t>
-  </si>
-  <si>
     <t>Transf 06/04</t>
   </si>
   <si>
@@ -1281,6 +1234,46 @@
   </si>
   <si>
     <t>Quienes adeudan ARBA deben abonar el monto coloreado en ROSADO si es que en el trancurso del mes 3 y 4 del 2026 no abonaron ninguna cuota.</t>
+  </si>
+  <si>
+    <t>Ferraro jose</t>
+  </si>
+  <si>
+    <t>Adjunto el comprobante de pago de las expensas netas de la cochera 30 , $58.102,08 07/05</t>
+  </si>
+  <si>
+    <t>Deposito $382.000 el 08/05:                                                                                                                                                                                                                                                                                                                                               Dto 2D.       53.453
+Dto 2F.        54.022
+Dto3A.        93.827
+Dto3C.       101.220
+               ———————-
+                    302.522.-
+Más              78.474.-
+                 ——————-
+                    382.000.-
+Las cocheras son 29/30/34/37/38/39
+6 X 13.079=78.474</t>
+  </si>
+  <si>
+    <t>El ultimo dia de abril el abono 102.165,29 para el 6E y 27.009,81 para la cochera 12 corregir</t>
+  </si>
+  <si>
+    <t>6E y Cochera 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local 2 </t>
+  </si>
+  <si>
+    <t>Pago $244.445 el 19/05</t>
+  </si>
+  <si>
+    <t>10B</t>
+  </si>
+  <si>
+    <t>IMPORTANTE!</t>
+  </si>
+  <si>
+    <t>10B en marzo pago $81.371,5 y se lo pusimos en ARBA cuando le tenia que quedar a favor en las expensas</t>
   </si>
 </sst>
 </file>
@@ -1509,7 +1502,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1596,12 +1589,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1621,6 +1608,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1991,7 +1996,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2301,13 +2306,8 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2318,38 +2318,34 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2374,9 +2370,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2385,6 +2378,42 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="19" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2509,18 +2538,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="22" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2534,6 +2551,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="28" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="28" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="28" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2563,60 +2610,25 @@
     <xf numFmtId="6" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="28" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="28" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="28" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2699,9 +2711,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2739,9 +2751,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2774,26 +2786,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2826,26 +2821,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3020,24 +2998,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R134"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="6" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="106"/>
       <c r="B1" s="115"/>
       <c r="C1" s="122" t="s">
@@ -3051,7 +3029,7 @@
       <c r="I1" s="104"/>
       <c r="J1" s="105"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="107"/>
       <c r="B2" s="116"/>
       <c r="C2" s="116" t="s">
@@ -3065,7 +3043,7 @@
       <c r="I2" s="117"/>
       <c r="J2" s="103"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="107"/>
       <c r="B3" s="116"/>
       <c r="C3" s="116" t="s">
@@ -3081,7 +3059,7 @@
       <c r="I3" s="117"/>
       <c r="J3" s="103"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="107"/>
       <c r="B4" s="116"/>
       <c r="C4" s="116" t="s">
@@ -3095,11 +3073,11 @@
       <c r="I4" s="117"/>
       <c r="J4" s="103"/>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="111"/>
       <c r="B5" s="116"/>
       <c r="C5" s="116" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="D5" s="116"/>
       <c r="E5" s="116" t="s">
@@ -3111,7 +3089,7 @@
       <c r="I5" s="116"/>
       <c r="J5" s="112"/>
     </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="111"/>
       <c r="B6" s="116"/>
       <c r="C6" s="116" t="s">
@@ -3125,7 +3103,7 @@
       <c r="I6" s="116"/>
       <c r="J6" s="112"/>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="113"/>
       <c r="B7" s="114"/>
       <c r="C7" s="114"/>
@@ -3137,118 +3115,118 @@
       <c r="I7" s="114"/>
       <c r="J7" s="118"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="275" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="286" t="s">
         <v>246</v>
       </c>
-      <c r="B14" s="275"/>
-      <c r="C14" s="275"/>
-      <c r="D14" s="275"/>
-      <c r="E14" s="275"/>
-      <c r="F14" s="275"/>
-      <c r="G14" s="275"/>
-      <c r="H14" s="275"/>
-      <c r="I14" s="275"/>
-      <c r="J14" s="275"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="275"/>
-      <c r="B15" s="275"/>
-      <c r="C15" s="275"/>
-      <c r="D15" s="275"/>
-      <c r="E15" s="275"/>
-      <c r="F15" s="275"/>
-      <c r="G15" s="275"/>
-      <c r="H15" s="275"/>
-      <c r="I15" s="275"/>
-      <c r="J15" s="275"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="275"/>
-      <c r="B16" s="275"/>
-      <c r="C16" s="275"/>
-      <c r="D16" s="275"/>
-      <c r="E16" s="275"/>
-      <c r="F16" s="275"/>
-      <c r="G16" s="275"/>
-      <c r="H16" s="275"/>
-      <c r="I16" s="275"/>
-      <c r="J16" s="275"/>
-    </row>
-    <row r="17" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="275"/>
-      <c r="B17" s="275"/>
-      <c r="C17" s="275"/>
-      <c r="D17" s="275"/>
-      <c r="E17" s="275"/>
-      <c r="F17" s="275"/>
-      <c r="G17" s="275"/>
-      <c r="H17" s="275"/>
-      <c r="I17" s="275"/>
-      <c r="J17" s="275"/>
-    </row>
-    <row r="18" spans="1:12" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="275"/>
-      <c r="B18" s="275"/>
-      <c r="C18" s="275"/>
-      <c r="D18" s="275"/>
-      <c r="E18" s="275"/>
-      <c r="F18" s="275"/>
-      <c r="G18" s="275"/>
-      <c r="H18" s="275"/>
-      <c r="I18" s="275"/>
-      <c r="J18" s="275"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="286"/>
+      <c r="C14" s="286"/>
+      <c r="D14" s="286"/>
+      <c r="E14" s="286"/>
+      <c r="F14" s="286"/>
+      <c r="G14" s="286"/>
+      <c r="H14" s="286"/>
+      <c r="I14" s="286"/>
+      <c r="J14" s="286"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="286"/>
+      <c r="B15" s="286"/>
+      <c r="C15" s="286"/>
+      <c r="D15" s="286"/>
+      <c r="E15" s="286"/>
+      <c r="F15" s="286"/>
+      <c r="G15" s="286"/>
+      <c r="H15" s="286"/>
+      <c r="I15" s="286"/>
+      <c r="J15" s="286"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="286"/>
+      <c r="B16" s="286"/>
+      <c r="C16" s="286"/>
+      <c r="D16" s="286"/>
+      <c r="E16" s="286"/>
+      <c r="F16" s="286"/>
+      <c r="G16" s="286"/>
+      <c r="H16" s="286"/>
+      <c r="I16" s="286"/>
+      <c r="J16" s="286"/>
+    </row>
+    <row r="17" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="286"/>
+      <c r="B17" s="286"/>
+      <c r="C17" s="286"/>
+      <c r="D17" s="286"/>
+      <c r="E17" s="286"/>
+      <c r="F17" s="286"/>
+      <c r="G17" s="286"/>
+      <c r="H17" s="286"/>
+      <c r="I17" s="286"/>
+      <c r="J17" s="286"/>
+    </row>
+    <row r="18" spans="1:12" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="286"/>
+      <c r="B18" s="286"/>
+      <c r="C18" s="286"/>
+      <c r="D18" s="286"/>
+      <c r="E18" s="286"/>
+      <c r="F18" s="286"/>
+      <c r="G18" s="286"/>
+      <c r="H18" s="286"/>
+      <c r="I18" s="286"/>
+      <c r="J18" s="286"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="H19" s="89"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="284" t="s">
-        <v>373</v>
-      </c>
-      <c r="B20" s="284"/>
-      <c r="C20" s="284"/>
-      <c r="D20" s="284"/>
-      <c r="E20" s="284"/>
-      <c r="F20" s="284"/>
-      <c r="G20" s="284"/>
-      <c r="H20" s="284"/>
-      <c r="I20" s="284"/>
-      <c r="J20" s="284"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="284"/>
-      <c r="B21" s="284"/>
-      <c r="C21" s="284"/>
-      <c r="D21" s="284"/>
-      <c r="E21" s="284"/>
-      <c r="F21" s="284"/>
-      <c r="G21" s="284"/>
-      <c r="H21" s="284"/>
-      <c r="I21" s="284"/>
-      <c r="J21" s="284"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="284"/>
-      <c r="B22" s="284"/>
-      <c r="C22" s="284"/>
-      <c r="D22" s="284"/>
-      <c r="E22" s="284"/>
-      <c r="F22" s="284"/>
-      <c r="G22" s="284"/>
-      <c r="H22" s="284"/>
-      <c r="I22" s="284"/>
-      <c r="J22" s="284"/>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="287" t="s">
+        <v>361</v>
+      </c>
+      <c r="B20" s="287"/>
+      <c r="C20" s="287"/>
+      <c r="D20" s="287"/>
+      <c r="E20" s="287"/>
+      <c r="F20" s="287"/>
+      <c r="G20" s="287"/>
+      <c r="H20" s="287"/>
+      <c r="I20" s="287"/>
+      <c r="J20" s="287"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="287"/>
+      <c r="B21" s="287"/>
+      <c r="C21" s="287"/>
+      <c r="D21" s="287"/>
+      <c r="E21" s="287"/>
+      <c r="F21" s="287"/>
+      <c r="G21" s="287"/>
+      <c r="H21" s="287"/>
+      <c r="I21" s="287"/>
+      <c r="J21" s="287"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="287"/>
+      <c r="B22" s="287"/>
+      <c r="C22" s="287"/>
+      <c r="D22" s="287"/>
+      <c r="E22" s="287"/>
+      <c r="F22" s="287"/>
+      <c r="G22" s="287"/>
+      <c r="H22" s="287"/>
+      <c r="I22" s="287"/>
+      <c r="J22" s="287"/>
+    </row>
+    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="89"/>
     </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
         <v>18</v>
       </c>
@@ -3274,7 +3252,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="232" t="s">
         <v>343</v>
       </c>
@@ -3289,7 +3267,7 @@
       <c r="J25" s="56"/>
       <c r="L25" s="67"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="31"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -3302,7 +3280,7 @@
       <c r="J26" s="5"/>
       <c r="L26" s="67"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="32" t="s">
         <v>36</v>
       </c>
@@ -3345,7 +3323,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="31" t="s">
         <v>235</v>
       </c>
@@ -3363,7 +3341,7 @@
       <c r="J28" s="56"/>
       <c r="L28" s="67"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -3376,7 +3354,7 @@
       <c r="J29" s="56"/>
       <c r="L29" s="67"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="32" t="s">
         <v>16</v>
       </c>
@@ -3404,7 +3382,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="31" t="s">
         <v>231</v>
       </c>
@@ -3419,13 +3397,13 @@
       <c r="J31" s="48"/>
       <c r="L31" s="67"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="34" t="s">
         <v>344</v>
       </c>
       <c r="B32" s="34"/>
-      <c r="C32" s="267" t="s">
-        <v>388</v>
+      <c r="C32" s="244" t="s">
+        <v>374</v>
       </c>
       <c r="D32" s="216">
         <v>5686514.7000000002</v>
@@ -3438,15 +3416,15 @@
       <c r="J32" s="48"/>
       <c r="L32" s="67"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="34" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="D33" s="216">
         <v>1609398</v>
@@ -3459,15 +3437,15 @@
       <c r="J33" s="48"/>
       <c r="L33" s="67"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="34" t="s">
         <v>234</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="D34" s="216">
         <v>1609398</v>
@@ -3480,12 +3458,12 @@
       <c r="J34" s="48"/>
       <c r="L34" s="67"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="34" t="s">
         <v>234</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C35" s="34" t="str">
         <f>C33</f>
@@ -3502,7 +3480,7 @@
       <c r="J35" s="48"/>
       <c r="L35" s="67"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="32" t="s">
         <v>233</v>
       </c>
@@ -3545,7 +3523,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="31" t="s">
         <v>1</v>
       </c>
@@ -3560,7 +3538,7 @@
       <c r="J37" s="5"/>
       <c r="L37" s="67"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -3573,7 +3551,7 @@
       <c r="J38" s="5"/>
       <c r="L38" s="67"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -3586,7 +3564,7 @@
       <c r="J39" s="5"/>
       <c r="L39" s="67"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="174"/>
@@ -3599,7 +3577,7 @@
       <c r="J40" s="5"/>
       <c r="L40" s="67"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="32" t="s">
         <v>232</v>
       </c>
@@ -3642,7 +3620,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="31" t="s">
         <v>223</v>
       </c>
@@ -3657,7 +3635,7 @@
       <c r="J42" s="35"/>
       <c r="L42" s="67"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>227</v>
       </c>
@@ -3698,11 +3676,11 @@
       </c>
       <c r="L43" s="67"/>
     </row>
-    <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="286" t="s">
+    <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="274" t="s">
         <v>227</v>
       </c>
-      <c r="B44" s="287"/>
+      <c r="B44" s="275"/>
       <c r="C44" s="5" t="s">
         <v>294</v>
       </c>
@@ -3736,7 +3714,7 @@
       <c r="K44" s="42"/>
       <c r="L44" s="67"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="32" t="s">
         <v>2</v>
       </c>
@@ -3779,7 +3757,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="31" t="s">
         <v>3</v>
       </c>
@@ -3794,15 +3772,15 @@
       <c r="J46" s="5"/>
       <c r="L46" s="67"/>
     </row>
-    <row r="47" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="69" t="s">
         <v>228</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="174" t="s">
-        <v>385</v>
-      </c>
-      <c r="D47" s="351">
+        <v>371</v>
+      </c>
+      <c r="D47" s="254">
         <v>1095070.23</v>
       </c>
       <c r="E47" s="66">
@@ -3840,15 +3818,15 @@
       <c r="M47" s="82"/>
       <c r="N47" s="82"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>229</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="174" t="s">
-        <v>382</v>
-      </c>
-      <c r="D48" s="351">
+        <v>370</v>
+      </c>
+      <c r="D48" s="254">
         <v>3904854.38</v>
       </c>
       <c r="E48" s="66">
@@ -3886,7 +3864,7 @@
       <c r="M48" s="82"/>
       <c r="N48" s="82"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>230</v>
       </c>
@@ -3923,13 +3901,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="174" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="D50" s="43">
         <v>359504.14</v>
@@ -3954,13 +3932,13 @@
       <c r="M50" s="82"/>
       <c r="N50" s="82"/>
     </row>
-    <row r="51" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="282" t="s">
-        <v>390</v>
+    <row r="51" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="271" t="s">
+        <v>376</v>
       </c>
       <c r="B51" s="288"/>
       <c r="C51" s="34" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="D51" s="43">
         <v>90000</v>
@@ -3991,13 +3969,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="34" t="s">
         <v>261</v>
       </c>
       <c r="B52" s="34"/>
       <c r="C52" s="174" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="D52" s="43">
         <v>6132.87</v>
@@ -4043,13 +4021,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="34" t="s">
         <v>262</v>
       </c>
       <c r="B53" s="34"/>
       <c r="C53" s="174" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="D53" s="43">
         <v>910081.41</v>
@@ -4080,7 +4058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="135" t="s">
         <v>260</v>
       </c>
@@ -4113,7 +4091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="32" t="s">
         <v>4</v>
       </c>
@@ -4160,7 +4138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -4173,7 +4151,7 @@
       <c r="J56" s="5"/>
       <c r="L56" s="67"/>
     </row>
-    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -4186,7 +4164,7 @@
       <c r="J57" s="5"/>
       <c r="L57" s="67"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="31" t="s">
         <v>224</v>
       </c>
@@ -4201,13 +4179,13 @@
       <c r="J58" s="5"/>
       <c r="L58" s="67"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="44" t="s">
         <v>342</v>
       </c>
       <c r="B59" s="184"/>
       <c r="C59" s="34" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="D59" s="43">
         <v>200000</v>
@@ -4230,13 +4208,13 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="44" t="s">
         <v>342</v>
       </c>
       <c r="B60" s="184"/>
       <c r="C60" s="34" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="D60" s="43">
         <v>200000</v>
@@ -4259,13 +4237,13 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="44" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="B61" s="184"/>
       <c r="C61" s="34" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="D61" s="43">
         <v>180000</v>
@@ -4303,13 +4281,13 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="286" t="s">
+    <row r="62" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="274" t="s">
         <v>341</v>
       </c>
-      <c r="B62" s="287"/>
+      <c r="B62" s="275"/>
       <c r="C62" s="130" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D62" s="43">
         <v>228448</v>
@@ -4347,13 +4325,13 @@
         <v>228448.00000000006</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="286" t="s">
-        <v>391</v>
-      </c>
-      <c r="B63" s="287"/>
+    <row r="63" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="274" t="s">
+        <v>377</v>
+      </c>
+      <c r="B63" s="275"/>
       <c r="C63" s="130" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="D63" s="43">
         <v>1471770</v>
@@ -4391,13 +4369,13 @@
         <v>1471769.9999999998</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="286" t="s">
-        <v>395</v>
-      </c>
-      <c r="B64" s="287"/>
+    <row r="64" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="274" t="s">
+        <v>381</v>
+      </c>
+      <c r="B64" s="275"/>
       <c r="C64" s="130" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="D64" s="43">
         <v>250000</v>
@@ -4420,13 +4398,13 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="286" t="s">
-        <v>379</v>
-      </c>
-      <c r="B65" s="287"/>
+    <row r="65" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="274" t="s">
+        <v>367</v>
+      </c>
+      <c r="B65" s="275"/>
       <c r="C65" s="130" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="D65" s="43">
         <v>46200</v>
@@ -4458,7 +4436,7 @@
       <c r="L65" s="67"/>
       <c r="M65" s="42"/>
     </row>
-    <row r="66" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="32" t="s">
         <v>225</v>
       </c>
@@ -4502,7 +4480,7 @@
       </c>
       <c r="N66" s="42"/>
     </row>
-    <row r="67" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -4515,7 +4493,7 @@
       <c r="J67" s="5"/>
       <c r="L67" s="67"/>
     </row>
-    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -4528,7 +4506,7 @@
       <c r="J68" s="5"/>
       <c r="L68" s="67"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="31" t="s">
         <v>5</v>
       </c>
@@ -4543,7 +4521,7 @@
       <c r="J69" s="5"/>
       <c r="L69" s="67"/>
     </row>
-    <row r="70" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="49" t="s">
         <v>6</v>
       </c>
@@ -4551,7 +4529,7 @@
         <v>35</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="D70" s="43">
         <v>860560</v>
@@ -4584,7 +4562,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="31"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -4616,7 +4594,7 @@
       <c r="L71" s="67"/>
       <c r="N71" s="43"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -4630,7 +4608,7 @@
       <c r="L72" s="67"/>
       <c r="N72" s="42"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="32" t="s">
         <v>7</v>
       </c>
@@ -4674,7 +4652,7 @@
       </c>
       <c r="N73" s="42"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>26</v>
       </c>
@@ -4710,7 +4688,7 @@
       </c>
       <c r="L74" s="67"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>27</v>
       </c>
@@ -4745,7 +4723,7 @@
       </c>
       <c r="L75" s="67"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="32" t="s">
         <v>226</v>
       </c>
@@ -4788,7 +4766,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="92"/>
       <c r="B77" s="92"/>
       <c r="C77" s="92"/>
@@ -4801,7 +4779,7 @@
       <c r="J77" s="92"/>
       <c r="L77" s="67"/>
     </row>
-    <row r="78" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="94" t="s">
         <v>295</v>
       </c>
@@ -4841,7 +4819,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="97"/>
       <c r="B79" s="98"/>
       <c r="C79" s="98"/>
@@ -4855,7 +4833,7 @@
       <c r="K79" s="42"/>
       <c r="L79" s="67"/>
     </row>
-    <row r="80" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>28</v>
       </c>
@@ -4902,7 +4880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D81" s="83"/>
       <c r="E81" s="42"/>
       <c r="F81" s="42"/>
@@ -4910,7 +4888,7 @@
       <c r="H81" s="42"/>
       <c r="I81" s="42"/>
     </row>
-    <row r="82" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="62" t="s">
         <v>37</v>
       </c>
@@ -4923,11 +4901,11 @@
       <c r="H82" s="42"/>
       <c r="I82" s="42"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="233" t="s">
-        <v>400</v>
-      </c>
-      <c r="C83" s="352">
+        <v>386</v>
+      </c>
+      <c r="C83" s="255">
         <v>24200</v>
       </c>
       <c r="D83" s="83"/>
@@ -4937,11 +4915,11 @@
       <c r="H83" s="42"/>
       <c r="I83" s="42"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="233" t="s">
-        <v>401</v>
-      </c>
-      <c r="C84" s="352">
+        <v>387</v>
+      </c>
+      <c r="C84" s="255">
         <f>90750/2</f>
         <v>45375</v>
       </c>
@@ -4952,11 +4930,11 @@
       <c r="H84" s="42"/>
       <c r="I84" s="42"/>
     </row>
-    <row r="85" spans="1:13" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="233" t="s">
-        <v>402</v>
-      </c>
-      <c r="C85" s="352">
+        <v>388</v>
+      </c>
+      <c r="C85" s="255">
         <f>90750/2</f>
         <v>45375</v>
       </c>
@@ -4967,7 +4945,7 @@
       <c r="H85" s="42"/>
       <c r="I85" s="42"/>
     </row>
-    <row r="86" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="63" t="s">
         <v>16</v>
       </c>
@@ -4983,27 +4961,27 @@
       <c r="H86" s="42"/>
       <c r="I86" s="42"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E87" s="42"/>
       <c r="F87" s="42"/>
       <c r="G87" s="42"/>
       <c r="H87" s="42"/>
       <c r="I87" s="42"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E88" s="58"/>
       <c r="F88" s="58"/>
       <c r="G88" s="58"/>
       <c r="H88" s="58"/>
       <c r="I88" s="58"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="280" t="s">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89" s="269" t="s">
         <v>32</v>
       </c>
-      <c r="B89" s="281"/>
-      <c r="C89" s="281"/>
-      <c r="D89" s="281"/>
+      <c r="B89" s="270"/>
+      <c r="C89" s="270"/>
+      <c r="D89" s="270"/>
       <c r="E89" s="78" t="s">
         <v>10</v>
       </c>
@@ -5023,9 +5001,9 @@
         <v>170</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="282"/>
-      <c r="B90" s="283"/>
+    <row r="90" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="271"/>
+      <c r="B90" s="272"/>
       <c r="C90" s="80"/>
       <c r="D90" s="43"/>
       <c r="E90" s="66">
@@ -5038,9 +5016,9 @@
       <c r="I90" s="66"/>
       <c r="J90" s="56"/>
     </row>
-    <row r="91" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="282"/>
-      <c r="B91" s="283"/>
+    <row r="91" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="271"/>
+      <c r="B91" s="272"/>
       <c r="C91" s="80"/>
       <c r="D91" s="43"/>
       <c r="E91" s="66"/>
@@ -5050,12 +5028,12 @@
       <c r="I91" s="66"/>
       <c r="J91" s="56"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A92" s="277" t="s">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A92" s="266" t="s">
         <v>16</v>
       </c>
-      <c r="B92" s="278"/>
-      <c r="C92" s="279"/>
+      <c r="B92" s="267"/>
+      <c r="C92" s="268"/>
       <c r="D92" s="77">
         <f>SUM(D90:D91)</f>
         <v>0</v>
@@ -5081,14 +5059,14 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E94" s="42"/>
       <c r="F94" s="42"/>
       <c r="G94" s="42"/>
       <c r="H94" s="42"/>
       <c r="I94" s="42"/>
     </row>
-    <row r="95" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="37" t="s">
         <v>29</v>
       </c>
@@ -5097,7 +5075,7 @@
         <v>21251305.129999999</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="39" t="s">
         <v>31</v>
       </c>
@@ -5105,45 +5083,45 @@
         <f>D80-D78</f>
         <v>21251305.129999999</v>
       </c>
-      <c r="D96" s="285" t="s">
+      <c r="D96" s="273" t="s">
         <v>286</v>
       </c>
-      <c r="E96" s="285"/>
-      <c r="F96" s="285"/>
-      <c r="G96" s="285"/>
-      <c r="H96" s="285"/>
-      <c r="I96" s="285"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D97" s="285"/>
-      <c r="E97" s="285"/>
-      <c r="F97" s="285"/>
-      <c r="G97" s="285"/>
-      <c r="H97" s="285"/>
-      <c r="I97" s="285"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D98" s="285"/>
-      <c r="E98" s="285"/>
-      <c r="F98" s="285"/>
-      <c r="G98" s="285"/>
-      <c r="H98" s="285"/>
-      <c r="I98" s="285"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E96" s="273"/>
+      <c r="F96" s="273"/>
+      <c r="G96" s="273"/>
+      <c r="H96" s="273"/>
+      <c r="I96" s="273"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D97" s="273"/>
+      <c r="E97" s="273"/>
+      <c r="F97" s="273"/>
+      <c r="G97" s="273"/>
+      <c r="H97" s="273"/>
+      <c r="I97" s="273"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D98" s="273"/>
+      <c r="E98" s="273"/>
+      <c r="F98" s="273"/>
+      <c r="G98" s="273"/>
+      <c r="H98" s="273"/>
+      <c r="I98" s="273"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="15" t="s">
         <v>19</v>
       </c>
       <c r="B99" s="16"/>
       <c r="C99" s="17"/>
-      <c r="D99" s="285"/>
-      <c r="E99" s="285"/>
-      <c r="F99" s="285"/>
-      <c r="G99" s="285"/>
-      <c r="H99" s="285"/>
-      <c r="I99" s="285"/>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D99" s="273"/>
+      <c r="E99" s="273"/>
+      <c r="F99" s="273"/>
+      <c r="G99" s="273"/>
+      <c r="H99" s="273"/>
+      <c r="I99" s="273"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="18" t="s">
         <v>20</v>
       </c>
@@ -5151,14 +5129,14 @@
         <v>12236086.148935104</v>
       </c>
       <c r="C100" s="19"/>
-      <c r="D100" s="285"/>
-      <c r="E100" s="285"/>
-      <c r="F100" s="285"/>
-      <c r="G100" s="285"/>
-      <c r="H100" s="285"/>
-      <c r="I100" s="285"/>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D100" s="273"/>
+      <c r="E100" s="273"/>
+      <c r="F100" s="273"/>
+      <c r="G100" s="273"/>
+      <c r="H100" s="273"/>
+      <c r="I100" s="273"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="20" t="s">
         <v>21</v>
       </c>
@@ -5169,14 +5147,14 @@
       <c r="C101" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="D101" s="285"/>
-      <c r="E101" s="285"/>
-      <c r="F101" s="285"/>
-      <c r="G101" s="285"/>
-      <c r="H101" s="285"/>
-      <c r="I101" s="285"/>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D101" s="273"/>
+      <c r="E101" s="273"/>
+      <c r="F101" s="273"/>
+      <c r="G101" s="273"/>
+      <c r="H101" s="273"/>
+      <c r="I101" s="273"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="20" t="s">
         <v>348</v>
       </c>
@@ -5185,29 +5163,29 @@
         <v>10374974.76</v>
       </c>
       <c r="C102" s="19"/>
-      <c r="D102" s="285"/>
-      <c r="E102" s="285"/>
-      <c r="F102" s="285"/>
-      <c r="G102" s="285"/>
-      <c r="H102" s="285"/>
-      <c r="I102" s="285"/>
-    </row>
-    <row r="103" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="358" t="s">
-        <v>411</v>
+      <c r="D102" s="273"/>
+      <c r="E102" s="273"/>
+      <c r="F102" s="273"/>
+      <c r="G102" s="273"/>
+      <c r="H102" s="273"/>
+      <c r="I102" s="273"/>
+    </row>
+    <row r="103" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="256" t="s">
+        <v>397</v>
       </c>
       <c r="B103" s="29">
         <v>-280064.46000000002</v>
       </c>
       <c r="C103" s="19"/>
-      <c r="D103" s="285"/>
-      <c r="E103" s="285"/>
-      <c r="F103" s="285"/>
-      <c r="G103" s="285"/>
-      <c r="H103" s="285"/>
-      <c r="I103" s="285"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D103" s="273"/>
+      <c r="E103" s="273"/>
+      <c r="F103" s="273"/>
+      <c r="G103" s="273"/>
+      <c r="H103" s="273"/>
+      <c r="I103" s="273"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="20" t="s">
         <v>34</v>
       </c>
@@ -5216,15 +5194,15 @@
         <v>-21251305.129999999</v>
       </c>
       <c r="C104" s="17"/>
-      <c r="D104" s="285"/>
-      <c r="E104" s="285"/>
-      <c r="F104" s="285"/>
-      <c r="G104" s="285"/>
-      <c r="H104" s="285"/>
-      <c r="I104" s="285"/>
+      <c r="D104" s="273"/>
+      <c r="E104" s="273"/>
+      <c r="F104" s="273"/>
+      <c r="G104" s="273"/>
+      <c r="H104" s="273"/>
+      <c r="I104" s="273"/>
       <c r="K104" s="43"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="20" t="s">
         <v>33</v>
       </c>
@@ -5233,31 +5211,31 @@
         <v>0</v>
       </c>
       <c r="C105" s="17"/>
-      <c r="D105" s="285"/>
-      <c r="E105" s="285"/>
-      <c r="F105" s="285"/>
-      <c r="G105" s="285"/>
-      <c r="H105" s="285"/>
-      <c r="I105" s="285"/>
+      <c r="D105" s="273"/>
+      <c r="E105" s="273"/>
+      <c r="F105" s="273"/>
+      <c r="G105" s="273"/>
+      <c r="H105" s="273"/>
+      <c r="I105" s="273"/>
       <c r="K105" s="51"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="20" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="B106" s="29">
         <v>90602</v>
       </c>
       <c r="C106" s="17"/>
-      <c r="D106" s="285"/>
-      <c r="E106" s="285"/>
-      <c r="F106" s="285"/>
-      <c r="G106" s="285"/>
-      <c r="H106" s="285"/>
-      <c r="I106" s="285"/>
+      <c r="D106" s="273"/>
+      <c r="E106" s="273"/>
+      <c r="F106" s="273"/>
+      <c r="G106" s="273"/>
+      <c r="H106" s="273"/>
+      <c r="I106" s="273"/>
       <c r="K106" s="51"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="20" t="s">
         <v>276</v>
       </c>
@@ -5266,15 +5244,15 @@
         <v>0</v>
       </c>
       <c r="C107" s="17"/>
-      <c r="D107" s="285"/>
-      <c r="E107" s="285"/>
-      <c r="F107" s="285"/>
-      <c r="G107" s="285"/>
-      <c r="H107" s="285"/>
-      <c r="I107" s="285"/>
+      <c r="D107" s="273"/>
+      <c r="E107" s="273"/>
+      <c r="F107" s="273"/>
+      <c r="G107" s="273"/>
+      <c r="H107" s="273"/>
+      <c r="I107" s="273"/>
       <c r="K107" s="51"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="20" t="s">
         <v>30</v>
       </c>
@@ -5283,14 +5261,14 @@
         <v>-113840</v>
       </c>
       <c r="C108" s="21"/>
-      <c r="D108" s="285"/>
-      <c r="E108" s="285"/>
-      <c r="F108" s="285"/>
-      <c r="G108" s="285"/>
-      <c r="H108" s="285"/>
-      <c r="I108" s="285"/>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D108" s="273"/>
+      <c r="E108" s="273"/>
+      <c r="F108" s="273"/>
+      <c r="G108" s="273"/>
+      <c r="H108" s="273"/>
+      <c r="I108" s="273"/>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="20" t="s">
         <v>37</v>
       </c>
@@ -5299,44 +5277,44 @@
         <v>-114950</v>
       </c>
       <c r="C109" s="21"/>
-      <c r="D109" s="285"/>
-      <c r="E109" s="285"/>
-      <c r="F109" s="285"/>
-      <c r="G109" s="285"/>
-      <c r="H109" s="285"/>
-      <c r="I109" s="285"/>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D109" s="273"/>
+      <c r="E109" s="273"/>
+      <c r="F109" s="273"/>
+      <c r="G109" s="273"/>
+      <c r="H109" s="273"/>
+      <c r="I109" s="273"/>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="20" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B110" s="81">
         <v>-673000</v>
       </c>
       <c r="C110" s="21"/>
-      <c r="D110" s="285"/>
-      <c r="E110" s="285"/>
-      <c r="F110" s="285"/>
-      <c r="G110" s="285"/>
-      <c r="H110" s="285"/>
-      <c r="I110" s="285"/>
-    </row>
-    <row r="111" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D110" s="273"/>
+      <c r="E110" s="273"/>
+      <c r="F110" s="273"/>
+      <c r="G110" s="273"/>
+      <c r="H110" s="273"/>
+      <c r="I110" s="273"/>
+    </row>
+    <row r="111" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="235" t="s">
-        <v>389</v>
-      </c>
-      <c r="B111" s="273">
+        <v>375</v>
+      </c>
+      <c r="B111" s="250">
         <v>-7428991</v>
       </c>
       <c r="C111" s="21"/>
-      <c r="D111" s="285"/>
-      <c r="E111" s="285"/>
-      <c r="F111" s="285"/>
-      <c r="G111" s="285"/>
-      <c r="H111" s="285"/>
-      <c r="I111" s="285"/>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D111" s="273"/>
+      <c r="E111" s="273"/>
+      <c r="F111" s="273"/>
+      <c r="G111" s="273"/>
+      <c r="H111" s="273"/>
+      <c r="I111" s="273"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="18" t="s">
         <v>23</v>
       </c>
@@ -5345,44 +5323,44 @@
         <v>4948144.8095401041</v>
       </c>
       <c r="C112" s="68"/>
-      <c r="D112" s="285"/>
-      <c r="E112" s="285"/>
-      <c r="F112" s="285"/>
-      <c r="G112" s="285"/>
-      <c r="H112" s="285"/>
-      <c r="I112" s="285"/>
-    </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D112" s="273"/>
+      <c r="E112" s="273"/>
+      <c r="F112" s="273"/>
+      <c r="G112" s="273"/>
+      <c r="H112" s="273"/>
+      <c r="I112" s="273"/>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113" s="21"/>
       <c r="C113" s="17"/>
-      <c r="D113" s="285"/>
-      <c r="E113" s="285"/>
-      <c r="F113" s="285"/>
-      <c r="G113" s="285"/>
-      <c r="H113" s="285"/>
-      <c r="I113" s="285"/>
-    </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D113" s="273"/>
+      <c r="E113" s="273"/>
+      <c r="F113" s="273"/>
+      <c r="G113" s="273"/>
+      <c r="H113" s="273"/>
+      <c r="I113" s="273"/>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114" s="15" t="s">
         <v>275</v>
       </c>
       <c r="B114" s="7"/>
       <c r="C114" s="17"/>
-      <c r="D114" s="285"/>
-      <c r="E114" s="285"/>
-      <c r="F114" s="285"/>
-      <c r="G114" s="285"/>
-      <c r="H114" s="285"/>
-      <c r="I114" s="285"/>
-    </row>
-    <row r="115" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="274"/>
+      <c r="D114" s="273"/>
+      <c r="E114" s="273"/>
+      <c r="F114" s="273"/>
+      <c r="G114" s="273"/>
+      <c r="H114" s="273"/>
+      <c r="I114" s="273"/>
+    </row>
+    <row r="115" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="251"/>
       <c r="B115" s="29"/>
       <c r="C115" s="17"/>
       <c r="D115" s="24"/>
       <c r="E115" s="24"/>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A116" s="35" t="s">
         <v>16</v>
       </c>
@@ -5393,17 +5371,17 @@
       <c r="C116" s="17"/>
       <c r="E116" s="24"/>
     </row>
-    <row r="117" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="21"/>
       <c r="C117" s="17"/>
       <c r="D117" s="24"/>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118" s="21"/>
       <c r="C118" s="17"/>
       <c r="D118" s="24"/>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C119" s="17"/>
       <c r="D119" s="42"/>
       <c r="E119" s="82"/>
@@ -5412,9 +5390,9 @@
       <c r="H119" s="82"/>
       <c r="I119" s="82"/>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120" s="15" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="B120" s="7">
         <v>325000</v>
@@ -5428,7 +5406,7 @@
       <c r="I120" s="82"/>
       <c r="J120" s="82"/>
     </row>
-    <row r="121" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="18" t="s">
         <v>241</v>
       </c>
@@ -5443,7 +5421,7 @@
       <c r="H121" s="86"/>
       <c r="I121" s="86"/>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122" s="18"/>
       <c r="B122" s="81"/>
       <c r="C122" s="23"/>
@@ -5454,7 +5432,7 @@
       <c r="H122" s="42"/>
       <c r="I122" s="42"/>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123" s="35" t="s">
         <v>16</v>
       </c>
@@ -5465,84 +5443,84 @@
       <c r="C123" s="23"/>
       <c r="D123" s="82"/>
     </row>
-    <row r="124" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C124" s="24"/>
       <c r="D124" s="82"/>
     </row>
-    <row r="125" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="347" t="s">
-        <v>407</v>
-      </c>
-      <c r="B125" s="353">
+    <row r="125" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="276" t="s">
+        <v>393</v>
+      </c>
+      <c r="B125" s="278">
         <f>B123+B112</f>
         <v>5386984.8095401041</v>
       </c>
       <c r="C125" s="17"/>
     </row>
-    <row r="126" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="348"/>
-      <c r="B126" s="354"/>
-    </row>
-    <row r="127" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="359" t="s">
-        <v>408</v>
-      </c>
-      <c r="B127" s="360"/>
+    <row r="126" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="277"/>
+      <c r="B126" s="279"/>
+    </row>
+    <row r="127" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="280" t="s">
+        <v>394</v>
+      </c>
+      <c r="B127" s="281"/>
       <c r="R127" s="8"/>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A128" s="361"/>
-      <c r="B128" s="362"/>
-    </row>
-    <row r="129" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="363"/>
-      <c r="B129" s="364"/>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B130" s="276"/>
-      <c r="C130" s="276"/>
-      <c r="D130" s="276"/>
-      <c r="E130" s="276"/>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A128" s="282"/>
+      <c r="B128" s="283"/>
+    </row>
+    <row r="129" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="284"/>
+      <c r="B129" s="285"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B130" s="265"/>
+      <c r="C130" s="265"/>
+      <c r="D130" s="265"/>
+      <c r="E130" s="265"/>
       <c r="F130" s="88"/>
       <c r="G130" s="88"/>
       <c r="H130" s="88"/>
       <c r="I130" s="88"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B131" s="276"/>
-      <c r="C131" s="276"/>
-      <c r="D131" s="276"/>
-      <c r="E131" s="276"/>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B131" s="265"/>
+      <c r="C131" s="265"/>
+      <c r="D131" s="265"/>
+      <c r="E131" s="265"/>
       <c r="F131" s="88"/>
       <c r="G131" s="88"/>
       <c r="H131" s="88"/>
       <c r="I131" s="88"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B132" s="276"/>
-      <c r="C132" s="276"/>
-      <c r="D132" s="276"/>
-      <c r="E132" s="276"/>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B132" s="265"/>
+      <c r="C132" s="265"/>
+      <c r="D132" s="265"/>
+      <c r="E132" s="265"/>
       <c r="F132" s="88"/>
       <c r="G132" s="88"/>
       <c r="H132" s="88"/>
       <c r="I132" s="88"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B133" s="276"/>
-      <c r="C133" s="276"/>
-      <c r="D133" s="276"/>
-      <c r="E133" s="276"/>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B133" s="265"/>
+      <c r="C133" s="265"/>
+      <c r="D133" s="265"/>
+      <c r="E133" s="265"/>
       <c r="F133" s="88"/>
       <c r="G133" s="88"/>
       <c r="H133" s="88"/>
       <c r="I133" s="88"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B134" s="276"/>
-      <c r="C134" s="276"/>
-      <c r="D134" s="276"/>
-      <c r="E134" s="276"/>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B134" s="265"/>
+      <c r="C134" s="265"/>
+      <c r="D134" s="265"/>
+      <c r="E134" s="265"/>
       <c r="F134" s="88"/>
       <c r="G134" s="88"/>
       <c r="H134" s="88"/>
@@ -5550,23 +5528,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A125:A126"/>
     <mergeCell ref="B125:B126"/>
     <mergeCell ref="A127:B129"/>
     <mergeCell ref="A14:J18"/>
+    <mergeCell ref="A20:J22"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A63:B63"/>
     <mergeCell ref="B130:E134"/>
     <mergeCell ref="A92:C92"/>
     <mergeCell ref="A89:D89"/>
     <mergeCell ref="A91:B91"/>
     <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A20:J22"/>
     <mergeCell ref="D96:I114"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A125:A126"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="90" orientation="landscape" r:id="rId1"/>
@@ -5577,30 +5555,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DJ154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" customWidth="1"/>
+    <col min="16" max="16" width="11.44140625" customWidth="1"/>
+    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="323" t="s">
         <v>305</v>
       </c>
@@ -5627,7 +5605,7 @@
       <c r="O1" s="152"/>
       <c r="P1" s="57"/>
     </row>
-    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="325"/>
       <c r="B2" s="326"/>
       <c r="C2" s="326"/>
@@ -5651,7 +5629,7 @@
       <c r="O2" s="153"/>
       <c r="P2" s="57"/>
     </row>
-    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="325"/>
       <c r="B3" s="326"/>
       <c r="C3" s="326"/>
@@ -5666,7 +5644,7 @@
       <c r="J3" s="154"/>
       <c r="K3" s="154"/>
       <c r="L3" s="182" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="223">
@@ -5675,7 +5653,7 @@
       <c r="O3" s="155"/>
       <c r="P3" s="14"/>
     </row>
-    <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="327"/>
       <c r="B4" s="328"/>
       <c r="C4" s="328"/>
@@ -5693,7 +5671,7 @@
       <c r="O4" s="159"/>
       <c r="P4" s="14"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="308" t="s">
@@ -5713,7 +5691,7 @@
       <c r="O5" s="310"/>
       <c r="P5" s="14"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="311"/>
@@ -5731,7 +5709,7 @@
       <c r="O6" s="313"/>
       <c r="P6" s="14"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="311"/>
@@ -5749,7 +5727,7 @@
       <c r="O7" s="313"/>
       <c r="P7" s="14"/>
     </row>
-    <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="314"/>
@@ -5767,7 +5745,7 @@
       <c r="O8" s="316"/>
       <c r="Q8" s="82"/>
     </row>
-    <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="317" t="s">
@@ -5793,7 +5771,7 @@
         <v>206250.11834400002</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="320"/>
@@ -5817,7 +5795,7 @@
         <v>244444.58470400001</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="292" t="s">
         <v>8</v>
       </c>
@@ -5849,7 +5827,7 @@
         <v>15</v>
       </c>
       <c r="K11" s="289" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="L11" s="289" t="s">
         <v>17</v>
@@ -5871,7 +5849,7 @@
         <v>231076.52147800004</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="293"/>
       <c r="B12" s="295"/>
       <c r="C12" s="293"/>
@@ -5895,7 +5873,7 @@
         <v>284548.77438200003</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="293"/>
       <c r="B13" s="295"/>
       <c r="C13" s="293"/>
@@ -5925,11 +5903,11 @@
         <v>332291.85733199993</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="253" t="s">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="243" t="s">
         <v>115</v>
       </c>
-      <c r="B14" s="253"/>
+      <c r="B14" s="243"/>
       <c r="C14" s="34" t="s">
         <v>110</v>
       </c>
@@ -5980,13 +5958,13 @@
       <c r="R14" s="298"/>
       <c r="S14" s="298"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="34" t="s">
+      <c r="C15" s="358" t="s">
         <v>114</v>
       </c>
-      <c r="D15" s="102" t="s">
+      <c r="D15" s="359" t="s">
         <v>303</v>
       </c>
       <c r="E15" s="180"/>
@@ -6030,7 +6008,7 @@
       <c r="R15" s="298"/>
       <c r="S15" s="298"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>115</v>
       </c>
@@ -6082,7 +6060,7 @@
       <c r="P16" s="109"/>
       <c r="S16" s="42"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>115</v>
       </c>
@@ -6129,7 +6107,7 @@
       <c r="P17" s="109"/>
       <c r="S17" s="42"/>
     </row>
-    <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>115</v>
       </c>
@@ -6147,7 +6125,7 @@
       <c r="G18" s="144">
         <v>661969.29652199999</v>
       </c>
-      <c r="H18" s="349">
+      <c r="H18" s="252">
         <f>701700</f>
         <v>701700</v>
       </c>
@@ -6179,7 +6157,7 @@
       <c r="P18" s="109"/>
       <c r="S18" s="42"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="55" t="s">
         <v>117</v>
       </c>
@@ -6197,7 +6175,7 @@
       <c r="G19" s="176">
         <v>225600.01</v>
       </c>
-      <c r="H19" s="350">
+      <c r="H19" s="253">
         <f>G19</f>
         <v>225600.01</v>
       </c>
@@ -6233,7 +6211,7 @@
       </c>
       <c r="S19" s="42"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="55" t="s">
         <v>118</v>
       </c>
@@ -6288,7 +6266,7 @@
       </c>
       <c r="S20" s="42"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="55" t="s">
         <v>117</v>
       </c>
@@ -6342,7 +6320,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="55" t="s">
         <v>119</v>
       </c>
@@ -6401,7 +6379,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="55" t="s">
         <v>119</v>
       </c>
@@ -6457,7 +6435,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="55" t="s">
         <v>119</v>
       </c>
@@ -6513,7 +6491,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="55" t="s">
         <v>117</v>
       </c>
@@ -6569,7 +6547,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="55" t="s">
         <v>118</v>
       </c>
@@ -6623,7 +6601,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="102" t="s">
         <v>117</v>
       </c>
@@ -6679,7 +6657,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="102" t="s">
         <v>119</v>
       </c>
@@ -6733,7 +6711,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="102" t="s">
         <v>119</v>
       </c>
@@ -6787,7 +6765,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="102" t="s">
         <v>119</v>
       </c>
@@ -6838,7 +6816,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="102" t="s">
         <v>117</v>
       </c>
@@ -6892,7 +6870,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="55" t="s">
         <v>118</v>
       </c>
@@ -6948,7 +6926,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A33" s="55" t="s">
         <v>117</v>
       </c>
@@ -7002,7 +6980,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A34" s="132" t="s">
         <v>119</v>
       </c>
@@ -7058,7 +7036,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="35" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A35" s="55" t="s">
         <v>119</v>
       </c>
@@ -7111,7 +7089,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A36" s="55" t="s">
         <v>119</v>
       </c>
@@ -7162,7 +7140,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A37" s="55" t="s">
         <v>117</v>
       </c>
@@ -7221,7 +7199,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A38" s="55" t="s">
         <v>118</v>
       </c>
@@ -7275,7 +7253,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="102" t="s">
         <v>117</v>
       </c>
@@ -7424,7 +7402,7 @@
       <c r="DI39" s="71"/>
       <c r="DJ39" s="71"/>
     </row>
-    <row r="40" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="102" t="s">
         <v>119</v>
       </c>
@@ -7575,7 +7553,7 @@
       <c r="DI40" s="71"/>
       <c r="DJ40" s="71"/>
     </row>
-    <row r="41" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="102" t="s">
         <v>119</v>
       </c>
@@ -7731,7 +7709,7 @@
       <c r="DI41" s="71"/>
       <c r="DJ41" s="71"/>
     </row>
-    <row r="42" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="102" t="s">
         <v>119</v>
       </c>
@@ -7882,7 +7860,7 @@
       <c r="DI42" s="71"/>
       <c r="DJ42" s="71"/>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A43" s="55" t="s">
         <v>117</v>
       </c>
@@ -7936,7 +7914,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A44" s="55" t="s">
         <v>118</v>
       </c>
@@ -7992,7 +7970,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A45" s="55" t="s">
         <v>117</v>
       </c>
@@ -8052,7 +8030,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A46" s="163" t="s">
         <v>119</v>
       </c>
@@ -8103,15 +8081,15 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A47" s="55" t="s">
         <v>119</v>
       </c>
       <c r="B47" s="5"/>
-      <c r="C47" s="34" t="s">
+      <c r="C47" s="258" t="s">
         <v>69</v>
       </c>
-      <c r="D47" s="102" t="s">
+      <c r="D47" s="259" t="s">
         <v>177</v>
       </c>
       <c r="E47" s="128" t="s">
@@ -8156,7 +8134,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A48" s="55" t="s">
         <v>119</v>
       </c>
@@ -8210,7 +8188,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="55" t="s">
         <v>117</v>
       </c>
@@ -8264,7 +8242,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="55" t="s">
         <v>118</v>
       </c>
@@ -8319,7 +8297,7 @@
       </c>
       <c r="Q50" s="42"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="55" t="s">
         <v>117</v>
       </c>
@@ -8374,7 +8352,7 @@
       </c>
       <c r="Q51" s="42"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="55" t="s">
         <v>119</v>
       </c>
@@ -8431,7 +8409,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="55" t="s">
         <v>119</v>
       </c>
@@ -8485,7 +8463,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="55" t="s">
         <v>119</v>
       </c>
@@ -8538,7 +8516,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" s="55" t="s">
         <v>117</v>
       </c>
@@ -8593,7 +8571,7 @@
       </c>
       <c r="R55" s="57"/>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="55" t="s">
         <v>118</v>
       </c>
@@ -8649,7 +8627,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="55" t="s">
         <v>117</v>
       </c>
@@ -8702,7 +8680,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="55" t="s">
         <v>119</v>
       </c>
@@ -8758,7 +8736,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="102" t="s">
         <v>119</v>
       </c>
@@ -8815,7 +8793,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="102" t="s">
         <v>119</v>
       </c>
@@ -8872,7 +8850,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="102" t="s">
         <v>117</v>
       </c>
@@ -8926,7 +8904,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="102" t="s">
         <v>118</v>
       </c>
@@ -8980,7 +8958,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="55" t="s">
         <v>117</v>
       </c>
@@ -9034,7 +9012,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="55" t="s">
         <v>119</v>
       </c>
@@ -9089,7 +9067,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" s="55" t="s">
         <v>119</v>
       </c>
@@ -9143,7 +9121,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" s="55" t="s">
         <v>119</v>
       </c>
@@ -9198,7 +9176,7 @@
       </c>
       <c r="S66" s="173"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" s="55" t="s">
         <v>117</v>
       </c>
@@ -9253,15 +9231,15 @@
       </c>
       <c r="S67" s="42"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="132" t="s">
         <v>118</v>
       </c>
       <c r="B68" s="131"/>
-      <c r="C68" s="34" t="s">
+      <c r="C68" s="360" t="s">
         <v>90</v>
       </c>
-      <c r="D68" s="102" t="s">
+      <c r="D68" s="361" t="s">
         <v>201</v>
       </c>
       <c r="E68" s="128"/>
@@ -9307,7 +9285,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="55" t="s">
         <v>117</v>
       </c>
@@ -9361,7 +9339,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="55" t="s">
         <v>119</v>
       </c>
@@ -9412,7 +9390,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="55" t="s">
         <v>119</v>
       </c>
@@ -9469,7 +9447,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="55" t="s">
         <v>119</v>
       </c>
@@ -9520,7 +9498,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="55" t="s">
         <v>120</v>
       </c>
@@ -9575,7 +9553,7 @@
       </c>
       <c r="Q73" s="71"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="55" t="s">
         <v>117</v>
       </c>
@@ -9629,7 +9607,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" s="55" t="s">
         <v>119</v>
       </c>
@@ -9683,7 +9661,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" s="55" t="s">
         <v>119</v>
       </c>
@@ -9738,7 +9716,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" s="102" t="s">
         <v>119</v>
       </c>
@@ -9789,7 +9767,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" s="102" t="s">
         <v>120</v>
       </c>
@@ -9843,7 +9821,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" s="55" t="s">
         <v>117</v>
       </c>
@@ -9897,7 +9875,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" s="55" t="s">
         <v>119</v>
       </c>
@@ -9948,7 +9926,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="55" t="s">
         <v>119</v>
       </c>
@@ -10004,7 +9982,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="55" t="s">
         <v>119</v>
       </c>
@@ -10061,7 +10039,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="55" t="s">
         <v>120</v>
       </c>
@@ -10115,7 +10093,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="55" t="s">
         <v>117</v>
       </c>
@@ -10169,7 +10147,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="55" t="s">
         <v>119</v>
       </c>
@@ -10223,7 +10201,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="55" t="s">
         <v>119</v>
       </c>
@@ -10277,7 +10255,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="102" t="s">
         <v>119</v>
       </c>
@@ -10331,7 +10309,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="102"/>
       <c r="B88" s="34"/>
       <c r="C88" s="34" t="s">
@@ -10383,7 +10361,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="102"/>
       <c r="B89" s="34"/>
       <c r="C89" s="34" t="s">
@@ -10435,7 +10413,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="102"/>
       <c r="B90" s="34"/>
       <c r="C90" s="34" t="s">
@@ -10487,7 +10465,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="102"/>
       <c r="B91" s="34"/>
       <c r="C91" s="34" t="s">
@@ -10539,7 +10517,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="102"/>
       <c r="B92" s="34"/>
       <c r="C92" s="167" t="s">
@@ -10594,7 +10572,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="102"/>
       <c r="B93" s="34"/>
       <c r="C93" s="34" t="s">
@@ -10643,7 +10621,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="102"/>
       <c r="B94" s="34"/>
       <c r="C94" s="34" t="s">
@@ -10695,7 +10673,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="102"/>
       <c r="B95" s="34"/>
       <c r="C95" s="34" t="s">
@@ -10747,7 +10725,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="102"/>
       <c r="B96" s="34"/>
       <c r="C96" s="34" t="s">
@@ -10799,7 +10777,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="102"/>
       <c r="B97" s="34"/>
       <c r="C97" s="34" t="s">
@@ -10848,7 +10826,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="102"/>
       <c r="B98" s="34"/>
       <c r="C98" s="34" t="s">
@@ -10900,7 +10878,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="102"/>
       <c r="B99" s="34"/>
       <c r="C99" s="34" t="s">
@@ -10952,7 +10930,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="102"/>
       <c r="B100" s="34"/>
       <c r="C100" s="34" t="s">
@@ -11004,7 +10982,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="102"/>
       <c r="B101" s="34"/>
       <c r="C101" s="34" t="s">
@@ -11053,7 +11031,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="102"/>
       <c r="B102" s="34"/>
       <c r="C102" s="34" t="s">
@@ -11105,7 +11083,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="102"/>
       <c r="B103" s="34"/>
       <c r="C103" s="34" t="s">
@@ -11157,7 +11135,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="102"/>
       <c r="B104" s="34"/>
       <c r="C104" s="34" t="s">
@@ -11209,7 +11187,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="102"/>
       <c r="B105" s="34"/>
       <c r="C105" s="34" t="s">
@@ -11261,7 +11239,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="102"/>
       <c r="B106" s="34"/>
       <c r="C106" s="34" t="s">
@@ -11310,7 +11288,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="102"/>
       <c r="B107" s="34"/>
       <c r="C107" s="34" t="s">
@@ -11362,7 +11340,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="102"/>
       <c r="B108" s="34"/>
       <c r="C108" s="34" t="s">
@@ -11414,7 +11392,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="102"/>
       <c r="B109" s="34"/>
       <c r="C109" s="34" t="s">
@@ -11466,7 +11444,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="102"/>
       <c r="B110" s="34"/>
       <c r="C110" s="34" t="s">
@@ -11517,7 +11495,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="102"/>
       <c r="B111" s="34"/>
       <c r="C111" s="34" t="s">
@@ -11569,7 +11547,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="102"/>
       <c r="B112" s="34"/>
       <c r="C112" s="34" t="s">
@@ -11621,7 +11599,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="102"/>
       <c r="B113" s="34"/>
       <c r="C113" s="34" t="s">
@@ -11673,7 +11651,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="102"/>
       <c r="B114" s="34"/>
       <c r="C114" s="34" t="s">
@@ -11725,7 +11703,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="102"/>
       <c r="B115" s="34"/>
       <c r="C115" s="34" t="s">
@@ -11777,7 +11755,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="102"/>
       <c r="B116" s="34"/>
       <c r="C116" s="34" t="s">
@@ -11831,7 +11809,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="102"/>
       <c r="B117" s="34"/>
       <c r="C117" s="34" t="s">
@@ -11841,7 +11819,7 @@
         <v>178</v>
       </c>
       <c r="E117" s="102" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="F117" s="136">
         <v>2.3E-3</v>
@@ -11885,7 +11863,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="102"/>
       <c r="B118" s="34"/>
       <c r="C118" s="34" t="s">
@@ -11942,7 +11920,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="121"/>
       <c r="B119" s="34"/>
       <c r="C119" s="34" t="s">
@@ -11994,7 +11972,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="121"/>
       <c r="B120" s="34"/>
       <c r="C120" s="34" t="s">
@@ -12046,7 +12024,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="121"/>
       <c r="B121" s="34"/>
       <c r="C121" s="34" t="s">
@@ -12056,7 +12034,7 @@
         <v>178</v>
       </c>
       <c r="E121" s="102" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="F121" s="136">
         <v>2.3E-3</v>
@@ -12100,7 +12078,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="121"/>
       <c r="B122" s="34"/>
       <c r="C122" s="34" t="s">
@@ -12152,7 +12130,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="121"/>
       <c r="B123" s="34"/>
       <c r="C123" s="34" t="s">
@@ -12201,7 +12179,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="121"/>
       <c r="B124" s="34"/>
       <c r="C124" s="34" t="s">
@@ -12256,7 +12234,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="166"/>
       <c r="B125" s="161"/>
       <c r="C125" s="34" t="s">
@@ -12310,7 +12288,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="166"/>
       <c r="B126" s="161"/>
       <c r="C126" s="34" t="s">
@@ -12362,7 +12340,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="121"/>
       <c r="B127" s="34"/>
       <c r="C127" s="34" t="s">
@@ -12414,7 +12392,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="121"/>
       <c r="B128" s="34"/>
       <c r="C128" s="34" t="s">
@@ -12466,7 +12444,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="121"/>
       <c r="B129" s="34"/>
       <c r="C129" s="34" t="s">
@@ -12518,7 +12496,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="121" t="s">
         <v>24</v>
       </c>
@@ -12572,7 +12550,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="121" t="s">
         <v>24</v>
       </c>
@@ -12626,7 +12604,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="52" t="s">
         <v>24</v>
       </c>
@@ -12645,7 +12623,7 @@
       <c r="N132" s="4"/>
       <c r="O132" s="7"/>
     </row>
-    <row r="133" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="26"/>
       <c r="B133" s="26"/>
       <c r="C133" s="26"/>
@@ -12687,13 +12665,13 @@
       </c>
       <c r="Q133" s="57"/>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="L134" s="59">
         <f>L133-M1</f>
         <v>-316178.57375999913</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C135" s="300"/>
       <c r="D135" s="300"/>
       <c r="E135" s="300"/>
@@ -12708,7 +12686,7 @@
       <c r="N135" s="300"/>
       <c r="O135" s="300"/>
     </row>
-    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="C136" s="300"/>
       <c r="D136" s="300"/>
       <c r="E136" s="300"/>
@@ -12723,7 +12701,7 @@
       <c r="N136" s="300"/>
       <c r="O136" s="300"/>
     </row>
-    <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="75"/>
       <c r="D137" s="75"/>
       <c r="E137" s="75"/>
@@ -12738,7 +12716,7 @@
       <c r="N137" s="75"/>
       <c r="O137" s="75"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C138" s="307" t="s">
         <v>246</v>
       </c>
@@ -12755,7 +12733,7 @@
       <c r="N138" s="307"/>
       <c r="O138" s="307"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C139" s="307"/>
       <c r="D139" s="307"/>
       <c r="E139" s="307"/>
@@ -12770,7 +12748,7 @@
       <c r="N139" s="307"/>
       <c r="O139" s="307"/>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C140" s="307"/>
       <c r="D140" s="307"/>
       <c r="E140" s="307"/>
@@ -12785,7 +12763,7 @@
       <c r="N140" s="307"/>
       <c r="O140" s="307"/>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C141" s="307"/>
       <c r="D141" s="307"/>
       <c r="E141" s="307"/>
@@ -12800,7 +12778,7 @@
       <c r="N141" s="307"/>
       <c r="O141" s="307"/>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C142" s="307"/>
       <c r="D142" s="307"/>
       <c r="E142" s="307"/>
@@ -12815,7 +12793,7 @@
       <c r="N142" s="307"/>
       <c r="O142" s="307"/>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C143" s="307"/>
       <c r="D143" s="307"/>
       <c r="E143" s="307"/>
@@ -12830,7 +12808,7 @@
       <c r="N143" s="307"/>
       <c r="O143" s="307"/>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C144" s="307"/>
       <c r="D144" s="307"/>
       <c r="E144" s="307"/>
@@ -12845,7 +12823,7 @@
       <c r="N144" s="307"/>
       <c r="O144" s="307"/>
     </row>
-    <row r="145" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C145" s="307"/>
       <c r="D145" s="307"/>
       <c r="E145" s="307"/>
@@ -12860,7 +12838,7 @@
       <c r="N145" s="307"/>
       <c r="O145" s="307"/>
     </row>
-    <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="75"/>
       <c r="D146" s="75"/>
       <c r="E146" s="75"/>
@@ -12875,7 +12853,7 @@
       <c r="N146" s="75"/>
       <c r="O146" s="75"/>
     </row>
-    <row r="147" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="75"/>
       <c r="D147" s="75"/>
       <c r="E147" s="75"/>
@@ -12890,7 +12868,7 @@
       <c r="N147" s="75"/>
       <c r="O147" s="75"/>
     </row>
-    <row r="148" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C148" s="299" t="s">
         <v>245</v>
       </c>
@@ -12907,7 +12885,7 @@
       <c r="N148" s="299"/>
       <c r="O148" s="299"/>
     </row>
-    <row r="149" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C149" s="299"/>
       <c r="D149" s="299"/>
       <c r="E149" s="299"/>
@@ -12922,7 +12900,7 @@
       <c r="N149" s="299"/>
       <c r="O149" s="299"/>
     </row>
-    <row r="150" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C150" s="299"/>
       <c r="D150" s="299"/>
       <c r="E150" s="299"/>
@@ -12941,7 +12919,7 @@
         <v>316178.57375999913</v>
       </c>
     </row>
-    <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C151" s="299"/>
       <c r="D151" s="299"/>
       <c r="E151" s="299"/>
@@ -12956,7 +12934,7 @@
       <c r="N151" s="299"/>
       <c r="O151" s="299"/>
     </row>
-    <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C152" s="299"/>
       <c r="D152" s="299"/>
       <c r="E152" s="299"/>
@@ -12971,7 +12949,7 @@
       <c r="N152" s="299"/>
       <c r="O152" s="299"/>
     </row>
-    <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C153" s="299"/>
       <c r="D153" s="299"/>
       <c r="E153" s="299"/>
@@ -12986,7 +12964,7 @@
       <c r="N153" s="299"/>
       <c r="O153" s="299"/>
     </row>
-    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C154" s="299"/>
       <c r="D154" s="299"/>
       <c r="E154" s="299"/>
@@ -13036,84 +13014,84 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AB47CA-548A-40FB-AC1D-01E96423736C}">
   <dimension ref="A1:DJ82"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="17.33203125" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="0.140625" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" customWidth="1"/>
-    <col min="13" max="13" width="16.5703125" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" customWidth="1"/>
-    <col min="15" max="15" width="19.5703125" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="17" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="0.109375" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" customWidth="1"/>
+    <col min="13" max="13" width="16.5546875" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" customWidth="1"/>
+    <col min="15" max="15" width="19.5546875" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" customWidth="1"/>
+    <col min="17" max="17" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="329" t="s">
+    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="340" t="s">
         <v>307</v>
       </c>
-      <c r="B1" s="329"/>
-      <c r="C1" s="329"/>
-      <c r="D1" s="329"/>
-      <c r="E1" s="329"/>
-      <c r="F1" s="329"/>
-      <c r="G1" s="329"/>
-      <c r="H1" s="329"/>
-      <c r="I1" s="329"/>
-      <c r="J1" s="329"/>
-      <c r="K1" s="329"/>
-      <c r="L1" s="329"/>
-      <c r="M1" s="329"/>
-      <c r="N1" s="329"/>
-      <c r="O1" s="330"/>
+      <c r="B1" s="340"/>
+      <c r="C1" s="340"/>
+      <c r="D1" s="340"/>
+      <c r="E1" s="340"/>
+      <c r="F1" s="340"/>
+      <c r="G1" s="340"/>
+      <c r="H1" s="340"/>
+      <c r="I1" s="340"/>
+      <c r="J1" s="340"/>
+      <c r="K1" s="340"/>
+      <c r="L1" s="340"/>
+      <c r="M1" s="340"/>
+      <c r="N1" s="340"/>
+      <c r="O1" s="341"/>
       <c r="R1" s="42"/>
     </row>
-    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="331"/>
-      <c r="B2" s="331"/>
-      <c r="C2" s="331"/>
-      <c r="D2" s="331"/>
-      <c r="E2" s="331"/>
-      <c r="F2" s="331"/>
-      <c r="G2" s="331"/>
-      <c r="H2" s="331"/>
-      <c r="I2" s="331"/>
-      <c r="J2" s="331"/>
-      <c r="K2" s="331"/>
-      <c r="L2" s="331"/>
-      <c r="M2" s="331"/>
-      <c r="N2" s="331"/>
-      <c r="O2" s="332"/>
+    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="342"/>
+      <c r="B2" s="342"/>
+      <c r="C2" s="342"/>
+      <c r="D2" s="342"/>
+      <c r="E2" s="342"/>
+      <c r="F2" s="342"/>
+      <c r="G2" s="342"/>
+      <c r="H2" s="342"/>
+      <c r="I2" s="342"/>
+      <c r="J2" s="342"/>
+      <c r="K2" s="342"/>
+      <c r="L2" s="342"/>
+      <c r="M2" s="342"/>
+      <c r="N2" s="342"/>
+      <c r="O2" s="343"/>
       <c r="R2" s="42"/>
     </row>
-    <row r="3" spans="1:27" s="230" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="365" t="s">
-        <v>412</v>
-      </c>
-      <c r="B3" s="366"/>
-      <c r="C3" s="366"/>
-      <c r="D3" s="366"/>
-      <c r="E3" s="366"/>
-      <c r="F3" s="366"/>
-      <c r="G3" s="366"/>
-      <c r="H3" s="366"/>
-      <c r="I3" s="366"/>
-      <c r="J3" s="366"/>
-      <c r="K3" s="366"/>
-      <c r="L3" s="366"/>
-      <c r="M3" s="366"/>
-      <c r="N3" s="366"/>
-      <c r="O3" s="367"/>
+    <row r="3" spans="1:27" s="230" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="337" t="s">
+        <v>398</v>
+      </c>
+      <c r="B3" s="338"/>
+      <c r="C3" s="338"/>
+      <c r="D3" s="338"/>
+      <c r="E3" s="338"/>
+      <c r="F3" s="338"/>
+      <c r="G3" s="338"/>
+      <c r="H3" s="338"/>
+      <c r="I3" s="338"/>
+      <c r="J3" s="338"/>
+      <c r="K3" s="338"/>
+      <c r="L3" s="338"/>
+      <c r="M3" s="338"/>
+      <c r="N3" s="338"/>
+      <c r="O3" s="339"/>
       <c r="P3" s="231"/>
       <c r="Q3" s="231"/>
       <c r="R3" s="231"/>
@@ -13127,7 +13105,7 @@
       <c r="Z3" s="231"/>
       <c r="AA3" s="231"/>
     </row>
-    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="292" t="s">
         <v>308</v>
       </c>
@@ -13155,11 +13133,11 @@
       <c r="I4" s="289" t="s">
         <v>349</v>
       </c>
-      <c r="J4" s="333" t="s">
+      <c r="J4" s="329" t="s">
         <v>335</v>
       </c>
       <c r="K4" s="124"/>
-      <c r="L4" s="355" t="s">
+      <c r="L4" s="334" t="s">
         <v>346</v>
       </c>
       <c r="M4" s="289" t="s">
@@ -13173,7 +13151,7 @@
       </c>
       <c r="R4" s="42"/>
     </row>
-    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="293"/>
       <c r="B5" s="293"/>
       <c r="C5" s="293"/>
@@ -13183,33 +13161,33 @@
       <c r="G5" s="290"/>
       <c r="H5" s="290"/>
       <c r="I5" s="290"/>
-      <c r="J5" s="334"/>
+      <c r="J5" s="330"/>
       <c r="K5" s="124"/>
-      <c r="L5" s="356"/>
+      <c r="L5" s="335"/>
       <c r="M5" s="290"/>
       <c r="N5" s="290"/>
       <c r="O5" s="290"/>
       <c r="R5" s="42"/>
     </row>
-    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="337"/>
-      <c r="B6" s="337"/>
-      <c r="C6" s="337"/>
-      <c r="D6" s="337"/>
-      <c r="E6" s="336"/>
-      <c r="F6" s="336"/>
-      <c r="G6" s="336"/>
-      <c r="H6" s="336"/>
-      <c r="I6" s="336"/>
-      <c r="J6" s="335"/>
+    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="333"/>
+      <c r="B6" s="333"/>
+      <c r="C6" s="333"/>
+      <c r="D6" s="333"/>
+      <c r="E6" s="332"/>
+      <c r="F6" s="332"/>
+      <c r="G6" s="332"/>
+      <c r="H6" s="332"/>
+      <c r="I6" s="332"/>
+      <c r="J6" s="331"/>
       <c r="K6" s="197"/>
-      <c r="L6" s="357"/>
-      <c r="M6" s="336"/>
-      <c r="N6" s="336"/>
-      <c r="O6" s="336"/>
+      <c r="L6" s="336"/>
+      <c r="M6" s="332"/>
+      <c r="N6" s="332"/>
+      <c r="O6" s="332"/>
       <c r="R6" s="42"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="198" t="s">
         <v>110</v>
       </c>
@@ -13244,7 +13222,7 @@
       <c r="K7" s="213">
         <v>-85849.897062580741</v>
       </c>
-      <c r="L7" s="350">
+      <c r="L7" s="253">
         <f>H7</f>
         <v>98532.35</v>
       </c>
@@ -13265,7 +13243,7 @@
       <c r="R7" s="298"/>
       <c r="S7" s="298"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="198" t="s">
         <v>315</v>
       </c>
@@ -13300,7 +13278,7 @@
       <c r="K8" s="139">
         <v>-300554.55212712329</v>
       </c>
-      <c r="L8" s="350"/>
+      <c r="L8" s="253"/>
       <c r="M8" s="178">
         <f t="shared" ref="M8:M69" si="3">IF(L8=H8,I8,J8)</f>
         <v>34751.71</v>
@@ -13320,7 +13298,7 @@
       <c r="R8" s="298"/>
       <c r="S8" s="298"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="198" t="s">
         <v>111</v>
       </c>
@@ -13355,7 +13333,7 @@
       <c r="K9" s="139">
         <v>-96183.680968261731</v>
       </c>
-      <c r="L9" s="350"/>
+      <c r="L9" s="253"/>
       <c r="M9" s="178">
         <f t="shared" si="3"/>
         <v>220785.72</v>
@@ -13374,7 +13352,7 @@
       </c>
       <c r="S9" s="42"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="198" t="s">
         <v>112</v>
       </c>
@@ -13409,7 +13387,7 @@
       <c r="K10" s="139">
         <v>-118441.06168819009</v>
       </c>
-      <c r="L10" s="350"/>
+      <c r="L10" s="253"/>
       <c r="M10" s="178">
         <f t="shared" si="3"/>
         <v>271876.73</v>
@@ -13428,7 +13406,7 @@
       </c>
       <c r="S10" s="42"/>
     </row>
-    <row r="11" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="202" t="s">
         <v>113</v>
       </c>
@@ -13463,7 +13441,7 @@
       <c r="K11" s="147">
         <v>-139108.62949955213</v>
       </c>
-      <c r="L11" s="349">
+      <c r="L11" s="252">
         <v>159659</v>
       </c>
       <c r="M11" s="178">
@@ -13483,7 +13461,7 @@
       </c>
       <c r="S11" s="42"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="205" t="s">
         <v>41</v>
       </c>
@@ -13520,7 +13498,7 @@
       <c r="K12" s="179">
         <v>-35723.479268552619</v>
       </c>
-      <c r="L12" s="350"/>
+      <c r="L12" s="253"/>
       <c r="M12" s="176">
         <v>0</v>
       </c>
@@ -13537,7 +13515,7 @@
       </c>
       <c r="S12" s="42"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="198" t="s">
         <v>42</v>
       </c>
@@ -13572,7 +13550,7 @@
       <c r="K13" s="140">
         <v>-13552.263311434101</v>
       </c>
-      <c r="L13" s="350">
+      <c r="L13" s="253">
         <f>H13</f>
         <v>103246.02</v>
       </c>
@@ -13593,7 +13571,7 @@
       </c>
       <c r="S13" s="42"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="198" t="s">
         <v>43</v>
       </c>
@@ -13630,7 +13608,7 @@
       <c r="K14" s="140">
         <v>-32267.293598652584</v>
       </c>
-      <c r="L14" s="350">
+      <c r="L14" s="253">
         <f>H14</f>
         <v>278569.03000000003</v>
       </c>
@@ -13650,7 +13628,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="198" t="s">
         <v>44</v>
       </c>
@@ -13687,7 +13665,7 @@
       <c r="K15" s="140">
         <v>-39458.119568728027</v>
       </c>
-      <c r="L15" s="350">
+      <c r="L15" s="253">
         <f>J15</f>
         <v>327283.03999999998</v>
       </c>
@@ -13707,7 +13685,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="198" t="s">
         <v>45</v>
       </c>
@@ -13742,7 +13720,7 @@
       <c r="K16" s="140">
         <v>-21834.202001754922</v>
       </c>
-      <c r="L16" s="350">
+      <c r="L16" s="253">
         <f>J16</f>
         <v>206069.05</v>
       </c>
@@ -13762,7 +13740,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A17" s="198" t="s">
         <v>46</v>
       </c>
@@ -13799,7 +13777,7 @@
       <c r="K17" s="140">
         <v>-39739.963279933261</v>
       </c>
-      <c r="L17" s="350">
+      <c r="L17" s="253">
         <f>J17</f>
         <v>329620.06</v>
       </c>
@@ -13819,7 +13797,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A18" s="198" t="s">
         <v>47</v>
       </c>
@@ -13856,7 +13834,7 @@
       <c r="K18" s="140">
         <v>-59469.023064297158</v>
       </c>
-      <c r="L18" s="350">
+      <c r="L18" s="253">
         <f>J18</f>
         <v>493262.07</v>
       </c>
@@ -13876,7 +13854,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A19" s="198" t="s">
         <v>48</v>
       </c>
@@ -13911,7 +13889,7 @@
       <c r="K19" s="140">
         <v>-46167.529954363912</v>
       </c>
-      <c r="L19" s="350">
+      <c r="L19" s="253">
         <f>H19</f>
         <v>73841.08</v>
       </c>
@@ -13931,7 +13909,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A20" s="198" t="s">
         <v>49</v>
       </c>
@@ -13966,7 +13944,7 @@
       <c r="K20" s="140">
         <v>-50450.024305730825</v>
       </c>
-      <c r="L20" s="350">
+      <c r="L20" s="253">
         <f>J20</f>
         <v>418454.09</v>
       </c>
@@ -13986,7 +13964,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="21" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A21" s="198" t="s">
         <v>50</v>
       </c>
@@ -14021,7 +13999,7 @@
       <c r="K21" s="140">
         <v>-58645.240752840618</v>
       </c>
-      <c r="L21" s="350">
+      <c r="L21" s="253">
         <f>J21</f>
         <v>187595.1</v>
       </c>
@@ -14041,7 +14019,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A22" s="198" t="s">
         <v>51</v>
       </c>
@@ -14076,7 +14054,7 @@
       <c r="K22" s="140">
         <v>-54278.041973373794</v>
       </c>
-      <c r="L22" s="350">
+      <c r="L22" s="253">
         <f>J22</f>
         <v>173625.11</v>
       </c>
@@ -14096,7 +14074,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A23" s="198" t="s">
         <v>52</v>
       </c>
@@ -14131,7 +14109,7 @@
       <c r="K23" s="140">
         <v>-59269.126292764471</v>
       </c>
-      <c r="L23" s="350"/>
+      <c r="L23" s="253"/>
       <c r="M23" s="176">
         <f t="shared" si="3"/>
         <v>189591.12</v>
@@ -14149,7 +14127,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A24" s="198" t="s">
         <v>53</v>
       </c>
@@ -14184,7 +14162,7 @@
       <c r="K24" s="140">
         <v>-26459.180750895117</v>
       </c>
-      <c r="L24" s="350">
+      <c r="L24" s="253">
         <f>J24</f>
         <v>403152.13</v>
       </c>
@@ -14204,7 +14182,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A25" s="198" t="s">
         <v>54</v>
       </c>
@@ -14239,7 +14217,7 @@
       <c r="K25" s="140">
         <v>-18320.652254346118</v>
       </c>
-      <c r="L25" s="350">
+      <c r="L25" s="253">
         <f>H25</f>
         <v>86455.14</v>
       </c>
@@ -14260,7 +14238,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A26" s="198" t="s">
         <v>55</v>
       </c>
@@ -14297,7 +14275,7 @@
       <c r="K26" s="140">
         <v>-35494.022958517773</v>
       </c>
-      <c r="L26" s="350">
+      <c r="L26" s="253">
         <f>H26</f>
         <v>270407.15000000002</v>
       </c>
@@ -14317,7 +14295,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A27" s="198" t="s">
         <v>56</v>
       </c>
@@ -14352,7 +14330,7 @@
       <c r="K27" s="140">
         <v>-58645.240752840618</v>
       </c>
-      <c r="L27" s="350"/>
+      <c r="L27" s="253"/>
       <c r="M27" s="176">
         <f t="shared" si="3"/>
         <v>187595.16</v>
@@ -14373,7 +14351,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="28" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A28" s="198" t="s">
         <v>57</v>
       </c>
@@ -14408,7 +14386,7 @@
       <c r="K28" s="140">
         <v>-54278.041973373794</v>
       </c>
-      <c r="L28" s="350">
+      <c r="L28" s="253">
         <f>H28</f>
         <v>86813.17</v>
       </c>
@@ -14428,7 +14406,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="29" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A29" s="198" t="s">
         <v>58</v>
       </c>
@@ -14463,7 +14441,7 @@
       <c r="K29" s="140">
         <v>-59269.126292764471</v>
       </c>
-      <c r="L29" s="350"/>
+      <c r="L29" s="253"/>
       <c r="M29" s="176">
         <f t="shared" si="3"/>
         <v>189591.18</v>
@@ -14481,7 +14459,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A30" s="198" t="s">
         <v>59</v>
       </c>
@@ -14516,7 +14494,7 @@
       <c r="K30" s="140">
         <v>-41158.725612503535</v>
       </c>
-      <c r="L30" s="350">
+      <c r="L30" s="253">
         <f>H30</f>
         <v>194226.19</v>
       </c>
@@ -14539,7 +14517,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="31" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A31" s="198" t="s">
         <v>60</v>
       </c>
@@ -14576,7 +14554,7 @@
       <c r="K31" s="140">
         <v>-27056.996275699232</v>
       </c>
-      <c r="L31" s="350">
+      <c r="L31" s="253">
         <f>J31</f>
         <v>224422.2</v>
       </c>
@@ -14596,7 +14574,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="198" t="s">
         <v>61</v>
       </c>
@@ -14633,7 +14611,7 @@
       <c r="K32" s="140">
         <v>-55523.211107424344</v>
       </c>
-      <c r="L32" s="350"/>
+      <c r="L32" s="253"/>
       <c r="M32" s="176">
         <f t="shared" si="3"/>
         <v>460534.21</v>
@@ -14749,7 +14727,7 @@
       <c r="DI32" s="71"/>
       <c r="DJ32" s="71"/>
     </row>
-    <row r="33" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="198" t="s">
         <v>62</v>
       </c>
@@ -14784,7 +14762,7 @@
       <c r="K33" s="140">
         <v>-58645.240752840618</v>
       </c>
-      <c r="L33" s="350"/>
+      <c r="L33" s="253"/>
       <c r="M33" s="176">
         <f t="shared" si="3"/>
         <v>187595.22</v>
@@ -14902,7 +14880,7 @@
       <c r="DI33" s="71"/>
       <c r="DJ33" s="71"/>
     </row>
-    <row r="34" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="198" t="s">
         <v>63</v>
       </c>
@@ -14939,7 +14917,7 @@
       <c r="K34" s="140">
         <v>-68627.40939162203</v>
       </c>
-      <c r="L34" s="350"/>
+      <c r="L34" s="253"/>
       <c r="M34" s="176">
         <v>0</v>
       </c>
@@ -15056,7 +15034,7 @@
       <c r="DI34" s="71"/>
       <c r="DJ34" s="71"/>
     </row>
-    <row r="35" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:114" s="133" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="198" t="s">
         <v>64</v>
       </c>
@@ -15091,7 +15069,7 @@
       <c r="K35" s="140">
         <v>-59269.126292764471</v>
       </c>
-      <c r="L35" s="350"/>
+      <c r="L35" s="253"/>
       <c r="M35" s="176">
         <f t="shared" si="3"/>
         <v>189591.24</v>
@@ -15207,7 +15185,7 @@
       <c r="DI35" s="71"/>
       <c r="DJ35" s="71"/>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A36" s="198" t="s">
         <v>65</v>
       </c>
@@ -15244,7 +15222,7 @@
       <c r="K36" s="140">
         <v>-37544.788729454507</v>
       </c>
-      <c r="L36" s="350">
+      <c r="L36" s="253">
         <f>H36</f>
         <v>226158.25</v>
       </c>
@@ -15264,7 +15242,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A37" s="198" t="s">
         <v>66</v>
       </c>
@@ -15299,7 +15277,7 @@
       <c r="K37" s="140">
         <v>-15441.692614377418</v>
       </c>
-      <c r="L37" s="350">
+      <c r="L37" s="253">
         <f>J37</f>
         <v>175787.26</v>
       </c>
@@ -15319,7 +15297,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A38" s="198" t="s">
         <v>67</v>
       </c>
@@ -15356,7 +15334,7 @@
       <c r="K38" s="140">
         <v>-44496.597872541868</v>
       </c>
-      <c r="L38" s="350">
+      <c r="L38" s="253">
         <f>H38</f>
         <v>235780.27</v>
       </c>
@@ -15382,7 +15360,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="39" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A39" s="198" t="s">
         <v>68</v>
       </c>
@@ -15419,7 +15397,7 @@
       <c r="K39" s="140">
         <v>-29363.23717477388</v>
       </c>
-      <c r="L39" s="350"/>
+      <c r="L39" s="253"/>
       <c r="M39" s="176">
         <v>238127.28000000003</v>
       </c>
@@ -15436,7 +15414,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="40" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A40" s="198" t="s">
         <v>69</v>
       </c>
@@ -15471,7 +15449,7 @@
       <c r="K40" s="140">
         <v>-21834.202001754922</v>
       </c>
-      <c r="L40" s="350">
+      <c r="L40" s="253">
         <f>J40</f>
         <v>206069.29</v>
       </c>
@@ -15491,7 +15469,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="41" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A41" s="198" t="s">
         <v>70</v>
       </c>
@@ -15526,7 +15504,7 @@
       <c r="K41" s="140">
         <v>-23841.94471455997</v>
       </c>
-      <c r="L41" s="350">
+      <c r="L41" s="253">
         <f>H41</f>
         <v>112509.3</v>
       </c>
@@ -15546,7 +15524,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A42" s="198" t="s">
         <v>71</v>
       </c>
@@ -15583,7 +15561,7 @@
       <c r="K42" s="140">
         <v>-54586.004053324927</v>
       </c>
-      <c r="L42" s="350">
+      <c r="L42" s="253">
         <f>H42</f>
         <v>217638.31</v>
       </c>
@@ -15603,7 +15581,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A43" s="198" t="s">
         <v>72</v>
       </c>
@@ -15640,7 +15618,7 @@
       <c r="K43" s="140">
         <v>-15488.300927353266</v>
       </c>
-      <c r="L43" s="350">
+      <c r="L43" s="253">
         <f>H43</f>
         <v>117996.32</v>
       </c>
@@ -15661,7 +15639,7 @@
       </c>
       <c r="Q43" s="42"/>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A44" s="198" t="s">
         <v>73</v>
       </c>
@@ -15698,7 +15676,7 @@
       <c r="K44" s="140">
         <v>-44496.597872541868</v>
       </c>
-      <c r="L44" s="350">
+      <c r="L44" s="253">
         <f>H44</f>
         <v>235780.33</v>
       </c>
@@ -15719,7 +15697,7 @@
       </c>
       <c r="Q44" s="42"/>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A45" s="198" t="s">
         <v>74</v>
       </c>
@@ -15754,7 +15732,7 @@
       <c r="K45" s="140">
         <v>-18872.781500367477</v>
       </c>
-      <c r="L45" s="350"/>
+      <c r="L45" s="253"/>
       <c r="M45" s="176">
         <f t="shared" si="3"/>
         <v>227368.34</v>
@@ -15775,7 +15753,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A46" s="198" t="s">
         <v>75</v>
       </c>
@@ -15810,7 +15788,7 @@
       <c r="K46" s="140">
         <v>-26270.852233588957</v>
       </c>
-      <c r="L46" s="350">
+      <c r="L46" s="253">
         <f>H46</f>
         <v>100816.35</v>
       </c>
@@ -15830,7 +15808,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A47" s="198" t="s">
         <v>76</v>
       </c>
@@ -15865,7 +15843,7 @@
       <c r="K47" s="140">
         <v>-19073.555771647982</v>
       </c>
-      <c r="L47" s="350">
+      <c r="L47" s="253">
         <f>J47</f>
         <v>229786.36</v>
       </c>
@@ -15885,7 +15863,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A48" s="198" t="s">
         <v>77</v>
       </c>
@@ -15922,7 +15900,7 @@
       <c r="K48" s="140">
         <v>-42237.887320636306</v>
       </c>
-      <c r="L48" s="350">
+      <c r="L48" s="253">
         <f>H48</f>
         <v>223812.37</v>
       </c>
@@ -15943,7 +15921,7 @@
       </c>
       <c r="R48" s="57"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="198" t="s">
         <v>78</v>
       </c>
@@ -15978,7 +15956,7 @@
       <c r="K49" s="140">
         <v>-20574.590917979629</v>
       </c>
-      <c r="L49" s="350">
+      <c r="L49" s="253">
         <f>H49</f>
         <v>85328.38</v>
       </c>
@@ -15998,7 +15976,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="198" t="s">
         <v>79</v>
       </c>
@@ -16035,7 +16013,7 @@
       <c r="K50" s="140">
         <v>-55523.211107424344</v>
       </c>
-      <c r="L50" s="350"/>
+      <c r="L50" s="253"/>
       <c r="M50" s="176">
         <f t="shared" si="3"/>
         <v>460534.39</v>
@@ -16053,7 +16031,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="198" t="s">
         <v>80</v>
       </c>
@@ -16088,7 +16066,7 @@
       <c r="K51" s="140">
         <v>-21231.879187913408</v>
       </c>
-      <c r="L51" s="350">
+      <c r="L51" s="253">
         <f>H51</f>
         <v>112504.4</v>
       </c>
@@ -16108,13 +16086,13 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="198" t="s">
         <v>81</v>
       </c>
       <c r="B52" s="199"/>
       <c r="C52" s="102" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="D52" s="129">
         <v>8.6999999999999994E-3</v>
@@ -16143,7 +16121,7 @@
       <c r="K52" s="140">
         <v>-21834.202001754922</v>
       </c>
-      <c r="L52" s="350">
+      <c r="L52" s="253">
         <f>J52</f>
         <v>206069.41</v>
       </c>
@@ -16166,7 +16144,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="198" t="s">
         <v>82</v>
       </c>
@@ -16203,7 +16181,7 @@
       <c r="K53" s="140">
         <v>-26652.784512487007</v>
       </c>
-      <c r="L53" s="350">
+      <c r="L53" s="253">
         <f>H53</f>
         <v>141229.42000000001</v>
       </c>
@@ -16226,7 +16204,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="198" t="s">
         <v>83</v>
       </c>
@@ -16263,7 +16241,7 @@
       <c r="K54" s="140">
         <v>-42237.887320636306</v>
       </c>
-      <c r="L54" s="350">
+      <c r="L54" s="253">
         <f>H54</f>
         <v>223812.43</v>
       </c>
@@ -16283,7 +16261,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="198" t="s">
         <v>84</v>
       </c>
@@ -16318,7 +16296,7 @@
       <c r="K55" s="140">
         <v>-16488.587028911512</v>
       </c>
-      <c r="L55" s="350">
+      <c r="L55" s="253">
         <f>H55</f>
         <v>87371.44</v>
       </c>
@@ -16338,7 +16316,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="198" t="s">
         <v>85</v>
       </c>
@@ -16375,7 +16353,7 @@
       <c r="K56" s="140">
         <v>-28251.808173042373</v>
       </c>
-      <c r="L56" s="350">
+      <c r="L56" s="253">
         <f>H56</f>
         <v>243903.45</v>
       </c>
@@ -16395,7 +16373,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="198" t="s">
         <v>86</v>
       </c>
@@ -16432,7 +16410,7 @@
       <c r="K57" s="140">
         <v>-26426.913457296439</v>
       </c>
-      <c r="L57" s="350">
+      <c r="L57" s="253">
         <f>J57</f>
         <v>280064.46000000002</v>
       </c>
@@ -16452,7 +16430,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="198" t="s">
         <v>87</v>
       </c>
@@ -16489,7 +16467,7 @@
       <c r="K58" s="140">
         <v>-27606.462301069463</v>
       </c>
-      <c r="L58" s="350">
+      <c r="L58" s="253">
         <f>J58</f>
         <v>260547.47</v>
       </c>
@@ -16509,7 +16487,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="198" t="s">
         <v>88</v>
       </c>
@@ -16546,7 +16524,7 @@
       <c r="K59" s="140">
         <v>-33257.557922213571</v>
       </c>
-      <c r="L59" s="350"/>
+      <c r="L59" s="253"/>
       <c r="M59" s="176">
         <f t="shared" si="3"/>
         <v>275853.48</v>
@@ -16565,7 +16543,7 @@
       </c>
       <c r="S59" s="173"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="198" t="s">
         <v>89</v>
       </c>
@@ -16602,7 +16580,7 @@
       <c r="K60" s="140">
         <v>-42237.887320636306</v>
       </c>
-      <c r="L60" s="350">
+      <c r="L60" s="253">
         <f>H60</f>
         <v>223812.49</v>
       </c>
@@ -16623,7 +16601,7 @@
       </c>
       <c r="S60" s="42"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="198" t="s">
         <v>90</v>
       </c>
@@ -16658,7 +16636,7 @@
       <c r="K61" s="140">
         <v>-16488.587028911512</v>
       </c>
-      <c r="L61" s="350"/>
+      <c r="L61" s="253"/>
       <c r="M61" s="176">
         <v>93370.5</v>
       </c>
@@ -16675,7 +16653,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="198" t="s">
         <v>91</v>
       </c>
@@ -16712,7 +16690,7 @@
       <c r="K62" s="140">
         <v>-46615.483485520119</v>
       </c>
-      <c r="L62" s="350">
+      <c r="L62" s="253">
         <f>H62</f>
         <v>234721.51</v>
       </c>
@@ -16732,7 +16710,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="198" t="s">
         <v>92</v>
       </c>
@@ -16767,7 +16745,7 @@
       <c r="K63" s="140">
         <v>-81340.722093700751</v>
       </c>
-      <c r="L63" s="350"/>
+      <c r="L63" s="253"/>
       <c r="M63" s="176">
         <v>0</v>
       </c>
@@ -16784,7 +16762,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="198" t="s">
         <v>93</v>
       </c>
@@ -16819,7 +16797,7 @@
       <c r="K64" s="140">
         <v>-21834.202001754922</v>
       </c>
-      <c r="L64" s="350">
+      <c r="L64" s="253">
         <f>H64</f>
         <v>103035.53</v>
       </c>
@@ -16842,7 +16820,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="198" t="s">
         <v>94</v>
       </c>
@@ -16879,7 +16857,7 @@
       <c r="K65" s="140">
         <v>-23691.364011099562</v>
       </c>
-      <c r="L65" s="350"/>
+      <c r="L65" s="253"/>
       <c r="M65" s="176">
         <f t="shared" si="3"/>
         <v>285419.53999999998</v>
@@ -16897,7 +16875,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="198" t="s">
         <v>95</v>
       </c>
@@ -16934,7 +16912,7 @@
       <c r="K66" s="140">
         <v>-41624.808742261725</v>
       </c>
-      <c r="L66" s="350">
+      <c r="L66" s="253">
         <f>H66</f>
         <v>317113.55</v>
       </c>
@@ -16955,7 +16933,7 @@
       </c>
       <c r="Q66" s="71"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="198" t="s">
         <v>96</v>
       </c>
@@ -16992,7 +16970,7 @@
       <c r="K67" s="140">
         <v>-42377.712259563734</v>
       </c>
-      <c r="L67" s="350">
+      <c r="L67" s="253">
         <f>H67</f>
         <v>236840.56</v>
       </c>
@@ -17012,7 +16990,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="198" t="s">
         <v>97</v>
       </c>
@@ -17038,7 +17016,7 @@
       <c r="K68" s="140">
         <v>-306490.57802999998</v>
       </c>
-      <c r="L68" s="350"/>
+      <c r="L68" s="253"/>
       <c r="M68" s="176">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -17056,7 +17034,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="198" t="s">
         <v>98</v>
       </c>
@@ -17091,7 +17069,7 @@
       <c r="K69" s="140">
         <v>-14036.272715413914</v>
       </c>
-      <c r="L69" s="350"/>
+      <c r="L69" s="253"/>
       <c r="M69" s="176">
         <f t="shared" si="3"/>
         <v>213867.58</v>
@@ -17109,7 +17087,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="198" t="s">
         <v>99</v>
       </c>
@@ -17146,7 +17124,7 @@
       <c r="K70" s="140">
         <v>-52250.939469883771</v>
       </c>
-      <c r="L70" s="350"/>
+      <c r="L70" s="253"/>
       <c r="M70" s="176">
         <v>0</v>
       </c>
@@ -17163,7 +17141,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="198" t="s">
         <v>100</v>
       </c>
@@ -17200,7 +17178,7 @@
       <c r="K71" s="140">
         <v>-293029.21731534239</v>
       </c>
-      <c r="L71" s="350">
+      <c r="L71" s="253">
         <f>330000+52822.6</f>
         <v>382822.6</v>
       </c>
@@ -17220,7 +17198,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="198" t="s">
         <v>101</v>
       </c>
@@ -17257,7 +17235,7 @@
       <c r="K72" s="140">
         <v>-49440.664302824298</v>
       </c>
-      <c r="L72" s="350">
+      <c r="L72" s="253">
         <f>H72</f>
         <v>233308.61</v>
       </c>
@@ -17277,7 +17255,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="198" t="s">
         <v>102</v>
       </c>
@@ -17312,7 +17290,7 @@
       <c r="K73" s="140">
         <v>-18198.753589640051</v>
       </c>
-      <c r="L73" s="350"/>
+      <c r="L73" s="253"/>
       <c r="M73" s="176">
         <f t="shared" ref="M73:M80" si="13">IF(L73=H73,I73,J73)</f>
         <v>228042.62</v>
@@ -17330,7 +17308,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="198" t="s">
         <v>103</v>
       </c>
@@ -17367,7 +17345,7 @@
       <c r="K74" s="140">
         <v>-21296.413775110734</v>
       </c>
-      <c r="L74" s="350"/>
+      <c r="L74" s="253"/>
       <c r="M74" s="176">
         <v>133429.63</v>
       </c>
@@ -17384,7 +17362,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="198" t="s">
         <v>104</v>
       </c>
@@ -17419,7 +17397,7 @@
       <c r="K75" s="140">
         <v>-19073.555771647982</v>
       </c>
-      <c r="L75" s="350"/>
+      <c r="L75" s="253"/>
       <c r="M75" s="176">
         <v>0</v>
       </c>
@@ -17436,7 +17414,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="198" t="s">
         <v>105</v>
       </c>
@@ -17473,7 +17451,7 @@
       <c r="K76" s="140">
         <v>-150580.49379336066</v>
       </c>
-      <c r="L76" s="350">
+      <c r="L76" s="253">
         <f>H76</f>
         <v>262636.65000000002</v>
       </c>
@@ -17493,7 +17471,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="198" t="s">
         <v>106</v>
       </c>
@@ -17530,7 +17508,7 @@
       <c r="K77" s="140">
         <v>-38139.941033607349</v>
       </c>
-      <c r="L77" s="350">
+      <c r="L77" s="253">
         <v>238359.66</v>
       </c>
       <c r="M77" s="176">
@@ -17550,7 +17528,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="198" t="s">
         <v>107</v>
       </c>
@@ -17587,7 +17565,7 @@
       <c r="K78" s="140">
         <v>-28108.397979270667</v>
       </c>
-      <c r="L78" s="350">
+      <c r="L78" s="253">
         <f>H78</f>
         <v>169316.67</v>
       </c>
@@ -17607,7 +17585,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="198" t="s">
         <v>108</v>
       </c>
@@ -17644,7 +17622,7 @@
       <c r="K79" s="140">
         <v>-18535.767545003793</v>
       </c>
-      <c r="L79" s="350">
+      <c r="L79" s="253">
         <f>H79</f>
         <v>134809.68</v>
       </c>
@@ -17664,7 +17642,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="198" t="s">
         <v>109</v>
       </c>
@@ -17719,7 +17697,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="34"/>
       <c r="B81" s="34"/>
       <c r="C81" s="102"/>
@@ -17736,7 +17714,7 @@
       <c r="N81" s="139"/>
       <c r="O81" s="140"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="26"/>
       <c r="B82" s="26"/>
       <c r="C82" s="26"/>
@@ -17777,7 +17755,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="M4:M6"/>
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A1:O2"/>
     <mergeCell ref="R7:S8"/>
@@ -17794,6 +17771,7 @@
     <mergeCell ref="H4:H6"/>
     <mergeCell ref="I4:I6"/>
     <mergeCell ref="L4:L6"/>
+    <mergeCell ref="M4:M6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" scale="110" orientation="landscape" r:id="rId1"/>
@@ -17802,664 +17780,529 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
-  <dimension ref="C2:M54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C1:M44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C3" s="237" t="s">
+    <row r="1" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C2" s="245" t="s">
         <v>353</v>
       </c>
-      <c r="D3" s="238">
+      <c r="D2" s="246">
         <v>1</v>
       </c>
-      <c r="E3" s="238"/>
-      <c r="F3" s="239"/>
-      <c r="G3" s="239"/>
-      <c r="H3" s="239"/>
-      <c r="I3" s="239"/>
-      <c r="J3" s="240"/>
-    </row>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C4" s="241" t="s">
+      <c r="E2" s="246"/>
+      <c r="F2" s="237"/>
+      <c r="G2" s="237"/>
+      <c r="H2" s="237"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+    </row>
+    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C3" s="247" t="s">
         <v>354</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="243">
-        <v>0</v>
+      <c r="D3" s="248"/>
+      <c r="E3" s="249">
+        <v>0</v>
+      </c>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71" t="s">
+        <v>355</v>
+      </c>
+      <c r="H3" s="239" t="s">
+        <v>399</v>
+      </c>
+      <c r="I3" s="240"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+    </row>
+    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C4" s="247" t="s">
+        <v>356</v>
+      </c>
+      <c r="D4" s="248" t="s">
+        <v>357</v>
+      </c>
+      <c r="E4" s="248" t="s">
+        <v>358</v>
       </c>
       <c r="F4" s="71"/>
       <c r="G4" s="71" t="s">
+        <v>359</v>
+      </c>
+      <c r="I4" s="240"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+    </row>
+    <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="233" t="s">
+        <v>360</v>
+      </c>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="242"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+    </row>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C6" s="344" t="s">
+        <v>400</v>
+      </c>
+      <c r="D6" s="345"/>
+      <c r="E6" s="345"/>
+      <c r="F6" s="345"/>
+      <c r="G6" s="345"/>
+      <c r="H6" s="345"/>
+      <c r="I6" s="345"/>
+      <c r="J6" s="346"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+    </row>
+    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C7" s="347"/>
+      <c r="D7" s="348"/>
+      <c r="E7" s="348"/>
+      <c r="F7" s="348"/>
+      <c r="G7" s="348"/>
+      <c r="H7" s="348"/>
+      <c r="I7" s="348"/>
+      <c r="J7" s="349"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+    </row>
+    <row r="8" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="350"/>
+      <c r="D8" s="351"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
+      <c r="G8" s="351"/>
+      <c r="H8" s="351"/>
+      <c r="I8" s="351"/>
+      <c r="J8" s="352"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
+    </row>
+    <row r="9" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="K9" s="71"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+    </row>
+    <row r="10" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="3:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="245" t="s">
+        <v>353</v>
+      </c>
+      <c r="D11" s="246">
+        <f>D2+1</f>
+        <v>2</v>
+      </c>
+      <c r="E11" s="246"/>
+      <c r="F11" s="237"/>
+      <c r="G11" s="237"/>
+      <c r="H11" s="237"/>
+      <c r="I11" s="237"/>
+      <c r="J11" s="238"/>
+      <c r="K11" s="257"/>
+    </row>
+    <row r="12" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C12" s="247" t="s">
+        <v>354</v>
+      </c>
+      <c r="D12" s="248"/>
+      <c r="E12" s="249">
+        <v>0</v>
+      </c>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71" t="s">
         <v>355</v>
       </c>
-      <c r="H4" s="244" t="s">
-        <v>362</v>
-      </c>
-      <c r="I4" s="245"/>
-      <c r="J4" s="246"/>
-    </row>
-    <row r="5" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C5" s="241" t="s">
+      <c r="H12" s="239" t="s">
+        <v>399</v>
+      </c>
+      <c r="I12" s="240"/>
+      <c r="J12" s="241"/>
+    </row>
+    <row r="13" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C13" s="247" t="s">
         <v>356</v>
       </c>
-      <c r="D5" s="242" t="s">
+      <c r="D13" s="248" t="s">
         <v>357</v>
       </c>
-      <c r="E5" s="242" t="s">
+      <c r="E13" s="248" t="s">
         <v>358</v>
-      </c>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="H5" t="s">
-        <v>361</v>
-      </c>
-      <c r="I5" s="245"/>
-      <c r="J5" s="246"/>
-    </row>
-    <row r="6" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="233" t="s">
-        <v>360</v>
-      </c>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="247"/>
-    </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="338" t="s">
-        <v>363</v>
-      </c>
-      <c r="D7" s="339"/>
-      <c r="E7" s="339"/>
-      <c r="F7" s="339"/>
-      <c r="G7" s="339"/>
-      <c r="H7" s="339"/>
-      <c r="I7" s="339"/>
-      <c r="J7" s="340"/>
-    </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C8" s="341"/>
-      <c r="D8" s="342"/>
-      <c r="E8" s="342"/>
-      <c r="F8" s="342"/>
-      <c r="G8" s="342"/>
-      <c r="H8" s="342"/>
-      <c r="I8" s="342"/>
-      <c r="J8" s="343"/>
-    </row>
-    <row r="9" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="344"/>
-      <c r="D9" s="345"/>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
-      <c r="G9" s="345"/>
-      <c r="H9" s="345"/>
-      <c r="I9" s="345"/>
-      <c r="J9" s="346"/>
-    </row>
-    <row r="11" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="248" t="s">
-        <v>353</v>
-      </c>
-      <c r="D12" s="249">
-        <f>D3+1</f>
-        <v>2</v>
-      </c>
-      <c r="E12" s="249"/>
-      <c r="F12" s="239"/>
-      <c r="G12" s="239"/>
-      <c r="H12" s="239"/>
-      <c r="I12" s="239"/>
-      <c r="J12" s="240"/>
-    </row>
-    <row r="13" spans="3:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="250" t="s">
-        <v>354</v>
-      </c>
-      <c r="D13" s="251"/>
-      <c r="E13" s="252">
-        <v>0</v>
       </c>
       <c r="F13" s="71"/>
       <c r="G13" s="71" t="s">
+        <v>359</v>
+      </c>
+      <c r="I13" s="240"/>
+      <c r="J13" s="241"/>
+    </row>
+    <row r="14" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C14" s="233" t="s">
+        <v>360</v>
+      </c>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="242"/>
+    </row>
+    <row r="15" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C15" s="344" t="s">
+        <v>401</v>
+      </c>
+      <c r="D15" s="345"/>
+      <c r="E15" s="345"/>
+      <c r="F15" s="345"/>
+      <c r="G15" s="345"/>
+      <c r="H15" s="345"/>
+      <c r="I15" s="345"/>
+      <c r="J15" s="346"/>
+    </row>
+    <row r="16" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C16" s="347"/>
+      <c r="D16" s="348"/>
+      <c r="E16" s="348"/>
+      <c r="F16" s="348"/>
+      <c r="G16" s="348"/>
+      <c r="H16" s="348"/>
+      <c r="I16" s="348"/>
+      <c r="J16" s="349"/>
+    </row>
+    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="350"/>
+      <c r="D17" s="351"/>
+      <c r="E17" s="351"/>
+      <c r="F17" s="351"/>
+      <c r="G17" s="351"/>
+      <c r="H17" s="351"/>
+      <c r="I17" s="351"/>
+      <c r="J17" s="352"/>
+    </row>
+    <row r="19" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="260" t="s">
+        <v>353</v>
+      </c>
+      <c r="D20" s="261">
+        <f>D11+1</f>
+        <v>3</v>
+      </c>
+      <c r="E20" s="261"/>
+      <c r="F20" s="237"/>
+      <c r="G20" s="237"/>
+      <c r="H20" s="237"/>
+      <c r="I20" s="237"/>
+      <c r="J20" s="238"/>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="262" t="s">
+        <v>354</v>
+      </c>
+      <c r="D21" s="263"/>
+      <c r="E21" s="264">
+        <v>0</v>
+      </c>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71" t="s">
         <v>355</v>
       </c>
-      <c r="H13" s="244"/>
-      <c r="I13" s="245"/>
-      <c r="J13" s="246"/>
-      <c r="K13" s="265"/>
-      <c r="L13" s="265"/>
-      <c r="M13" s="265"/>
-    </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C14" s="250" t="s">
+      <c r="H21" s="239" t="s">
+        <v>288</v>
+      </c>
+      <c r="I21" s="240"/>
+      <c r="J21" s="241"/>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="262" t="s">
         <v>356</v>
       </c>
-      <c r="D14" s="251" t="s">
+      <c r="D22" s="263" t="s">
         <v>357</v>
       </c>
-      <c r="E14" s="251" t="s">
+      <c r="E22" s="263" t="s">
         <v>358</v>
-      </c>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="H14" t="s">
-        <v>364</v>
-      </c>
-      <c r="I14" s="245"/>
-      <c r="J14" s="246"/>
-      <c r="K14" s="265"/>
-      <c r="L14" s="265"/>
-      <c r="M14" s="265"/>
-    </row>
-    <row r="15" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="233" t="s">
-        <v>360</v>
-      </c>
-      <c r="D15" s="71"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="247"/>
-      <c r="K15" s="265"/>
-      <c r="L15" s="265"/>
-      <c r="M15" s="265"/>
-    </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="338" t="s">
-        <v>365</v>
-      </c>
-      <c r="D16" s="339"/>
-      <c r="E16" s="339"/>
-      <c r="F16" s="339"/>
-      <c r="G16" s="339"/>
-      <c r="H16" s="339"/>
-      <c r="I16" s="339"/>
-      <c r="J16" s="340"/>
-      <c r="K16" s="265"/>
-      <c r="L16" s="265"/>
-      <c r="M16" s="265"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C17" s="341"/>
-      <c r="D17" s="342"/>
-      <c r="E17" s="342"/>
-      <c r="F17" s="342"/>
-      <c r="G17" s="342"/>
-      <c r="H17" s="342"/>
-      <c r="I17" s="342"/>
-      <c r="J17" s="343"/>
-      <c r="K17" s="265"/>
-      <c r="L17" s="265"/>
-      <c r="M17" s="265"/>
-    </row>
-    <row r="18" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="344"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
-      <c r="G18" s="345"/>
-      <c r="H18" s="345"/>
-      <c r="I18" s="345"/>
-      <c r="J18" s="346"/>
-      <c r="K18" s="265"/>
-      <c r="L18" s="265"/>
-      <c r="M18" s="265"/>
-    </row>
-    <row r="20" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C21" s="254" t="s">
-        <v>353</v>
-      </c>
-      <c r="D21" s="255">
-        <f>D12+1</f>
-        <v>3</v>
-      </c>
-      <c r="E21" s="255"/>
-      <c r="F21" s="239"/>
-      <c r="G21" s="239"/>
-      <c r="H21" s="239"/>
-      <c r="I21" s="239"/>
-      <c r="J21" s="240"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C22" s="256" t="s">
-        <v>354</v>
-      </c>
-      <c r="D22" s="257"/>
-      <c r="E22" s="258">
-        <v>0</v>
       </c>
       <c r="F22" s="71"/>
       <c r="G22" s="71" t="s">
+        <v>359</v>
+      </c>
+      <c r="H22" s="263" t="s">
+        <v>403</v>
+      </c>
+      <c r="I22" s="240"/>
+      <c r="J22" s="241"/>
+    </row>
+    <row r="23" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C23" s="233" t="s">
+        <v>360</v>
+      </c>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="242"/>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="344" t="s">
+        <v>402</v>
+      </c>
+      <c r="D24" s="345"/>
+      <c r="E24" s="345"/>
+      <c r="F24" s="345"/>
+      <c r="G24" s="345"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="345"/>
+      <c r="J24" s="346"/>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="347"/>
+      <c r="D25" s="348"/>
+      <c r="E25" s="348"/>
+      <c r="F25" s="348"/>
+      <c r="G25" s="348"/>
+      <c r="H25" s="348"/>
+      <c r="I25" s="348"/>
+      <c r="J25" s="349"/>
+    </row>
+    <row r="26" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C26" s="350"/>
+      <c r="D26" s="351"/>
+      <c r="E26" s="351"/>
+      <c r="F26" s="351"/>
+      <c r="G26" s="351"/>
+      <c r="H26" s="351"/>
+      <c r="I26" s="351"/>
+      <c r="J26" s="352"/>
+    </row>
+    <row r="28" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="353" t="s">
+        <v>353</v>
+      </c>
+      <c r="D29" s="354">
+        <f>D20+1</f>
+        <v>4</v>
+      </c>
+      <c r="E29" s="354"/>
+      <c r="F29" s="237"/>
+      <c r="G29" s="237"/>
+      <c r="H29" s="237"/>
+      <c r="I29" s="237"/>
+      <c r="J29" s="238"/>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="355" t="s">
+        <v>354</v>
+      </c>
+      <c r="D30" s="356"/>
+      <c r="E30" s="357">
+        <v>0</v>
+      </c>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71" t="s">
         <v>355</v>
       </c>
-      <c r="H22" s="244"/>
-      <c r="I22" s="245"/>
-      <c r="J22" s="246"/>
-      <c r="K22" s="265"/>
-      <c r="L22" s="265"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C23" s="256" t="s">
+      <c r="H30" s="239" t="s">
+        <v>404</v>
+      </c>
+      <c r="I30" s="240"/>
+      <c r="J30" s="241"/>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="355" t="s">
         <v>356</v>
       </c>
-      <c r="D23" s="257" t="s">
+      <c r="D31" s="356" t="s">
         <v>357</v>
       </c>
-      <c r="E23" s="257" t="s">
+      <c r="E31" s="356" t="s">
         <v>358</v>
-      </c>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="H23" t="s">
-        <v>366</v>
-      </c>
-      <c r="I23" s="245"/>
-      <c r="J23" s="246"/>
-      <c r="K23" s="265"/>
-      <c r="L23" s="265"/>
-    </row>
-    <row r="24" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="233" t="s">
-        <v>360</v>
-      </c>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="247"/>
-      <c r="K24" s="265"/>
-      <c r="L24" s="265"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C25" s="338" t="s">
-        <v>367</v>
-      </c>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
-      <c r="G25" s="339"/>
-      <c r="H25" s="339"/>
-      <c r="I25" s="339"/>
-      <c r="J25" s="340"/>
-      <c r="K25" s="265"/>
-      <c r="L25" s="265"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C26" s="341"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
-      <c r="G26" s="342"/>
-      <c r="H26" s="342"/>
-      <c r="I26" s="342"/>
-      <c r="J26" s="343"/>
-      <c r="K26" s="265"/>
-      <c r="L26" s="265"/>
-    </row>
-    <row r="27" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="344"/>
-      <c r="D27" s="345"/>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
-      <c r="G27" s="345"/>
-      <c r="H27" s="345"/>
-      <c r="I27" s="345"/>
-      <c r="J27" s="346"/>
-    </row>
-    <row r="29" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C30" s="106" t="s">
-        <v>353</v>
-      </c>
-      <c r="D30" s="104">
-        <f>D21+1</f>
-        <v>4</v>
-      </c>
-      <c r="E30" s="104"/>
-      <c r="F30" s="239"/>
-      <c r="G30" s="239"/>
-      <c r="H30" s="239"/>
-      <c r="I30" s="239"/>
-      <c r="J30" s="240"/>
-      <c r="K30" s="265"/>
-      <c r="L30" s="265"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C31" s="259" t="s">
-        <v>354</v>
-      </c>
-      <c r="D31" s="260"/>
-      <c r="E31" s="261">
-        <v>0</v>
       </c>
       <c r="F31" s="71"/>
       <c r="G31" s="71" t="s">
+        <v>359</v>
+      </c>
+      <c r="H31" s="71" t="s">
+        <v>404</v>
+      </c>
+      <c r="I31" s="240"/>
+      <c r="J31" s="241"/>
+    </row>
+    <row r="32" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C32" s="233" t="s">
+        <v>360</v>
+      </c>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="242"/>
+    </row>
+    <row r="33" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C33" s="344" t="s">
+        <v>405</v>
+      </c>
+      <c r="D33" s="345"/>
+      <c r="E33" s="345"/>
+      <c r="F33" s="345"/>
+      <c r="G33" s="345"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="345"/>
+      <c r="J33" s="346"/>
+    </row>
+    <row r="34" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C34" s="347"/>
+      <c r="D34" s="348"/>
+      <c r="E34" s="348"/>
+      <c r="F34" s="348"/>
+      <c r="G34" s="348"/>
+      <c r="H34" s="348"/>
+      <c r="I34" s="348"/>
+      <c r="J34" s="349"/>
+    </row>
+    <row r="35" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C35" s="350"/>
+      <c r="D35" s="351"/>
+      <c r="E35" s="351"/>
+      <c r="F35" s="351"/>
+      <c r="G35" s="351"/>
+      <c r="H35" s="351"/>
+      <c r="I35" s="351"/>
+      <c r="J35" s="352"/>
+    </row>
+    <row r="37" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C38" s="362" t="s">
+        <v>353</v>
+      </c>
+      <c r="D38" s="363">
+        <f>D29+1</f>
+        <v>5</v>
+      </c>
+      <c r="E38" s="363"/>
+      <c r="F38" s="237"/>
+      <c r="G38" s="237"/>
+      <c r="H38" s="237"/>
+      <c r="I38" s="237"/>
+      <c r="J38" s="238"/>
+    </row>
+    <row r="39" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C39" s="364" t="s">
+        <v>354</v>
+      </c>
+      <c r="D39" s="365"/>
+      <c r="E39" s="366">
+        <v>0</v>
+      </c>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71" t="s">
         <v>355</v>
       </c>
-      <c r="H31" s="244" t="s">
-        <v>370</v>
-      </c>
-      <c r="I31" s="245"/>
-      <c r="J31" s="246"/>
-      <c r="K31" s="265"/>
-      <c r="L31" s="265"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C32" s="259" t="s">
+      <c r="H39" s="239" t="s">
+        <v>406</v>
+      </c>
+      <c r="I39" s="240"/>
+      <c r="J39" s="241"/>
+    </row>
+    <row r="40" spans="3:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="C40" s="364" t="s">
         <v>356</v>
       </c>
-      <c r="D32" s="260" t="s">
+      <c r="D40" s="365" t="s">
         <v>357</v>
       </c>
-      <c r="E32" s="260" t="s">
+      <c r="E40" s="365" t="s">
         <v>358</v>
-      </c>
-      <c r="F32" s="71"/>
-      <c r="G32" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="H32" t="s">
-        <v>369</v>
-      </c>
-      <c r="I32" s="245"/>
-      <c r="J32" s="246"/>
-      <c r="K32" s="265"/>
-      <c r="L32" s="265"/>
-    </row>
-    <row r="33" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="233" t="s">
-        <v>360</v>
-      </c>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="71"/>
-      <c r="J33" s="247"/>
-      <c r="K33" s="265"/>
-      <c r="L33" s="265"/>
-    </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C34" s="338" t="s">
-        <v>368</v>
-      </c>
-      <c r="D34" s="339"/>
-      <c r="E34" s="339"/>
-      <c r="F34" s="339"/>
-      <c r="G34" s="339"/>
-      <c r="H34" s="339"/>
-      <c r="I34" s="339"/>
-      <c r="J34" s="340"/>
-      <c r="K34" s="265"/>
-      <c r="L34" s="265"/>
-    </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C35" s="341"/>
-      <c r="D35" s="342"/>
-      <c r="E35" s="342"/>
-      <c r="F35" s="342"/>
-      <c r="G35" s="342"/>
-      <c r="H35" s="342"/>
-      <c r="I35" s="342"/>
-      <c r="J35" s="343"/>
-      <c r="K35" s="265"/>
-      <c r="L35" s="265"/>
-    </row>
-    <row r="36" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="344"/>
-      <c r="D36" s="345"/>
-      <c r="E36" s="345"/>
-      <c r="F36" s="345"/>
-      <c r="G36" s="345"/>
-      <c r="H36" s="345"/>
-      <c r="I36" s="345"/>
-      <c r="J36" s="346"/>
-    </row>
-    <row r="38" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C39" s="262" t="s">
-        <v>353</v>
-      </c>
-      <c r="D39" s="263">
-        <f>D30+1</f>
-        <v>5</v>
-      </c>
-      <c r="E39" s="263"/>
-      <c r="F39" s="239"/>
-      <c r="G39" s="239"/>
-      <c r="H39" s="239"/>
-      <c r="I39" s="239"/>
-      <c r="J39" s="240"/>
-      <c r="K39" s="265"/>
-      <c r="L39" s="265"/>
-    </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C40" s="264" t="s">
-        <v>354</v>
-      </c>
-      <c r="D40" s="265"/>
-      <c r="E40" s="266">
-        <v>0</v>
       </c>
       <c r="F40" s="71"/>
       <c r="G40" s="71" t="s">
-        <v>355</v>
-      </c>
-      <c r="H40" s="244"/>
-      <c r="I40" s="245"/>
-      <c r="J40" s="246"/>
-      <c r="K40" s="265"/>
-      <c r="L40" s="265"/>
-    </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C41" s="264" t="s">
-        <v>356</v>
-      </c>
-      <c r="D41" s="265" t="s">
-        <v>357</v>
-      </c>
-      <c r="E41" s="265" t="s">
-        <v>358</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="H40" s="71" t="s">
+        <v>406</v>
+      </c>
+      <c r="I40" s="367" t="s">
+        <v>407</v>
+      </c>
+      <c r="J40" s="368"/>
+    </row>
+    <row r="41" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C41" s="233" t="s">
+        <v>360</v>
+      </c>
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
       <c r="F41" s="71"/>
-      <c r="G41" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="H41" t="s">
-        <v>371</v>
-      </c>
-      <c r="I41" s="245"/>
-      <c r="J41" s="246"/>
-      <c r="K41" s="265"/>
-      <c r="L41" s="265"/>
-    </row>
-    <row r="42" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="233" t="s">
-        <v>360</v>
-      </c>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="71"/>
-      <c r="I42" s="71"/>
-      <c r="J42" s="247"/>
-      <c r="K42" s="265"/>
-      <c r="L42" s="265"/>
-    </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C43" s="338" t="s">
-        <v>372</v>
-      </c>
-      <c r="D43" s="339"/>
-      <c r="E43" s="339"/>
-      <c r="F43" s="339"/>
-      <c r="G43" s="339"/>
-      <c r="H43" s="339"/>
-      <c r="I43" s="339"/>
-      <c r="J43" s="340"/>
-      <c r="K43" s="265"/>
-      <c r="L43" s="265"/>
-    </row>
-    <row r="44" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C44" s="341"/>
-      <c r="D44" s="342"/>
-      <c r="E44" s="342"/>
-      <c r="F44" s="342"/>
-      <c r="G44" s="342"/>
-      <c r="H44" s="342"/>
-      <c r="I44" s="342"/>
-      <c r="J44" s="343"/>
-      <c r="K44" s="265"/>
-      <c r="L44" s="265"/>
-    </row>
-    <row r="45" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="344"/>
-      <c r="D45" s="345"/>
-      <c r="E45" s="345"/>
-      <c r="F45" s="345"/>
-      <c r="G45" s="345"/>
-      <c r="H45" s="345"/>
-      <c r="I45" s="345"/>
-      <c r="J45" s="346"/>
-      <c r="K45" s="265"/>
-      <c r="L45" s="265"/>
-    </row>
-    <row r="47" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="48" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C48" s="268" t="s">
-        <v>353</v>
-      </c>
-      <c r="D48" s="269">
-        <f>D39+1</f>
-        <v>6</v>
-      </c>
-      <c r="E48" s="269"/>
-      <c r="F48" s="239"/>
-      <c r="G48" s="239"/>
-      <c r="H48" s="239"/>
-      <c r="I48" s="239"/>
-      <c r="J48" s="240"/>
-      <c r="K48" s="265"/>
-      <c r="L48" s="265"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C49" s="270" t="s">
-        <v>354</v>
-      </c>
-      <c r="D49" s="271"/>
-      <c r="E49" s="272">
-        <v>0</v>
-      </c>
-      <c r="F49" s="71"/>
-      <c r="G49" s="71" t="s">
-        <v>355</v>
-      </c>
-      <c r="H49" s="244"/>
-      <c r="I49" s="245"/>
-      <c r="J49" s="246"/>
-      <c r="K49" s="265"/>
-      <c r="L49" s="265"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C50" s="270" t="s">
-        <v>356</v>
-      </c>
-      <c r="D50" s="271" t="s">
-        <v>357</v>
-      </c>
-      <c r="E50" s="271" t="s">
-        <v>358</v>
-      </c>
-      <c r="F50" s="71"/>
-      <c r="G50" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="H50" t="s">
-        <v>383</v>
-      </c>
-      <c r="I50" s="245"/>
-      <c r="J50" s="246"/>
-      <c r="K50" s="265"/>
-      <c r="L50" s="265"/>
-    </row>
-    <row r="51" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="233" t="s">
-        <v>360</v>
-      </c>
-      <c r="D51" s="71"/>
-      <c r="E51" s="71"/>
-      <c r="F51" s="71"/>
-      <c r="G51" s="71"/>
-      <c r="H51" s="71"/>
-      <c r="I51" s="71"/>
-      <c r="J51" s="247"/>
-      <c r="K51" s="265"/>
-      <c r="L51" s="265"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C52" s="338" t="s">
-        <v>384</v>
-      </c>
-      <c r="D52" s="339"/>
-      <c r="E52" s="339"/>
-      <c r="F52" s="339"/>
-      <c r="G52" s="339"/>
-      <c r="H52" s="339"/>
-      <c r="I52" s="339"/>
-      <c r="J52" s="340"/>
-      <c r="K52" s="265"/>
-      <c r="L52" s="265"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C53" s="341"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-      <c r="G53" s="342"/>
-      <c r="H53" s="342"/>
-      <c r="I53" s="342"/>
-      <c r="J53" s="343"/>
-      <c r="K53" s="265"/>
-      <c r="L53" s="265"/>
-    </row>
-    <row r="54" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="344"/>
-      <c r="D54" s="345"/>
-      <c r="E54" s="345"/>
-      <c r="F54" s="345"/>
-      <c r="G54" s="345"/>
-      <c r="H54" s="345"/>
-      <c r="I54" s="345"/>
-      <c r="J54" s="346"/>
-      <c r="K54" s="265"/>
-      <c r="L54" s="265"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="242"/>
+    </row>
+    <row r="42" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C42" s="344" t="s">
+        <v>408</v>
+      </c>
+      <c r="D42" s="345"/>
+      <c r="E42" s="345"/>
+      <c r="F42" s="345"/>
+      <c r="G42" s="345"/>
+      <c r="H42" s="345"/>
+      <c r="I42" s="345"/>
+      <c r="J42" s="346"/>
+    </row>
+    <row r="43" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C43" s="347"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
+      <c r="G43" s="348"/>
+      <c r="H43" s="348"/>
+      <c r="I43" s="348"/>
+      <c r="J43" s="349"/>
+    </row>
+    <row r="44" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C44" s="350"/>
+      <c r="D44" s="351"/>
+      <c r="E44" s="351"/>
+      <c r="F44" s="351"/>
+      <c r="G44" s="351"/>
+      <c r="H44" s="351"/>
+      <c r="I44" s="351"/>
+      <c r="J44" s="352"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="C52:J54"/>
-    <mergeCell ref="C7:J9"/>
-    <mergeCell ref="C16:J18"/>
-    <mergeCell ref="C25:J27"/>
-    <mergeCell ref="C34:J36"/>
-    <mergeCell ref="C43:J45"/>
+    <mergeCell ref="C15:J17"/>
+    <mergeCell ref="C6:J8"/>
+    <mergeCell ref="C24:J26"/>
+    <mergeCell ref="C33:J35"/>
+    <mergeCell ref="C42:J44"/>
+    <mergeCell ref="I40:J40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
